--- a/AAII_Financials/Quarterly/EH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
   <si>
     <t>EH</t>
   </si>
@@ -656,339 +656,364 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F8" s="3">
         <v>1400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>3300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>7600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>10500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>5300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>3000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>8600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>5300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>5000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>5400</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F9" s="3">
         <v>600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1100</v>
-      </c>
-      <c r="F9" s="3">
-        <v>700</v>
-      </c>
-      <c r="G9" s="3">
-        <v>400</v>
       </c>
       <c r="H9" s="3">
         <v>700</v>
       </c>
       <c r="I9" s="3">
+        <v>400</v>
+      </c>
+      <c r="J9" s="3">
+        <v>700</v>
+      </c>
+      <c r="K9" s="3">
         <v>300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>3100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>4300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>2200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>3400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>2500</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F10" s="3">
         <v>800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>700</v>
       </c>
       <c r="H10" s="3">
         <v>1400</v>
       </c>
       <c r="I10" s="3">
+        <v>800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K10" s="3">
         <v>500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>4500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>6200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>3000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>5200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>2900</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,82 +1040,90 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E12" s="3">
         <v>5200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>5200</v>
+      </c>
+      <c r="G12" s="3">
         <v>7500</v>
       </c>
-      <c r="F12" s="3">
-        <v>5100</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I12" s="3">
         <v>4300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>4800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>4400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>5400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>5500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>4500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>4000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>7100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>2600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>2600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>2400</v>
-      </c>
-      <c r="S12" s="3">
-        <v>2200</v>
-      </c>
-      <c r="T12" s="3">
-        <v>4200</v>
       </c>
       <c r="U12" s="3">
         <v>2200</v>
       </c>
       <c r="V12" s="3">
+        <v>4200</v>
+      </c>
+      <c r="W12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="X12" s="3">
         <v>2000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>3900</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,8 +1196,14 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1237,8 +1276,14 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1311,8 +1356,14 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1387,170 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>11800</v>
+      <c r="D17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E17" s="3">
-        <v>13500</v>
+        <v>13700</v>
       </c>
       <c r="F17" s="3">
-        <v>14900</v>
+        <v>11900</v>
       </c>
       <c r="G17" s="3">
-        <v>11300</v>
+        <v>13600</v>
       </c>
       <c r="H17" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>11400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="K17" s="3">
+        <v>9600</v>
+      </c>
+      <c r="L17" s="3">
+        <v>15900</v>
+      </c>
+      <c r="M17" s="3">
         <v>12300</v>
       </c>
-      <c r="I17" s="3">
-        <v>9600</v>
-      </c>
-      <c r="J17" s="3">
-        <v>15900</v>
-      </c>
-      <c r="K17" s="3">
-        <v>12300</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>12400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>12800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>14400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>10700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>8100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>6300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>8200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>7000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>10800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>4800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>5100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>9000</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="M18" s="3">
         <v>-10400</v>
       </c>
-      <c r="E18" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-12700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-14600</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-10400</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-10600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-9500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-6800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-3300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-5800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-3200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-3500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-3600</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,82 +1577,90 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>600</v>
+      </c>
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-2200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
       </c>
       <c r="Q20" s="3">
         <v>200</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>200</v>
+      </c>
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1609,59 +1682,65 @@
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>-13300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-10000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-8700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-6100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-3800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-1300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-5300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-3000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-4400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-3200</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1669,16 +1748,16 @@
         <v>100</v>
       </c>
       <c r="E22" s="3">
+        <v>100</v>
+      </c>
+      <c r="F22" s="3">
+        <v>100</v>
+      </c>
+      <c r="G22" s="3">
         <v>1800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>100</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
@@ -1711,10 +1790,10 @@
         <v>100</v>
       </c>
       <c r="S22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1725,91 +1804,103 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-10200</v>
+        <v>-10100</v>
       </c>
       <c r="E23" s="3">
-        <v>-12000</v>
+        <v>-9300</v>
       </c>
       <c r="F23" s="3">
-        <v>-15200</v>
+        <v>-10300</v>
       </c>
       <c r="G23" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="I23" s="3">
         <v>-10600</v>
       </c>
-      <c r="H23" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="K23" s="3">
         <v>-9500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-14400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-10300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-10600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-9000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-7000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-3200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-5800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-3300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-4700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-3600</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1856,14 +1947,14 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -1871,19 +1962,25 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2053,174 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-10200</v>
+      <c r="D26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E26" s="3">
-        <v>-12000</v>
+        <v>-9300</v>
       </c>
       <c r="F26" s="3">
-        <v>-15200</v>
+        <v>-10300</v>
       </c>
       <c r="G26" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="N26" s="3">
         <v>-10600</v>
       </c>
-      <c r="H26" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-9000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-7100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-3200</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-1600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-5800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-3300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-4700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-3700</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-10400</v>
+      <c r="D27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E27" s="3">
-        <v>-12000</v>
+        <v>-9300</v>
       </c>
       <c r="F27" s="3">
-        <v>-15200</v>
+        <v>-10500</v>
       </c>
       <c r="G27" s="3">
-        <v>-10500</v>
+        <v>-12100</v>
       </c>
       <c r="H27" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="J27" s="3">
         <v>-10200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-9500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-14600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-10200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-10600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-8900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-6800</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-3100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-6000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-3400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-4100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-4000</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2293,14 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2373,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2453,14 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,156 +2533,174 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>2200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
       </c>
       <c r="Q32" s="3">
         <v>-200</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-10400</v>
+      <c r="D33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E33" s="3">
-        <v>-12000</v>
+        <v>-9300</v>
       </c>
       <c r="F33" s="3">
-        <v>-15200</v>
+        <v>-10500</v>
       </c>
       <c r="G33" s="3">
-        <v>-10500</v>
+        <v>-12100</v>
       </c>
       <c r="H33" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="J33" s="3">
         <v>-10200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-9500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-14600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-10200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-10600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-8900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-6800</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-6000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-3400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-4100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-4000</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2773,179 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-10400</v>
+      <c r="D35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E35" s="3">
-        <v>-12000</v>
+        <v>-9300</v>
       </c>
       <c r="F35" s="3">
-        <v>-15200</v>
+        <v>-10500</v>
       </c>
       <c r="G35" s="3">
-        <v>-10500</v>
+        <v>-12100</v>
       </c>
       <c r="H35" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="J35" s="3">
         <v>-10200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-9500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-14600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-10200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-10600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-8900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-6800</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-6000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-3400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-4100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-4000</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2972,10 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,68 +3002,70 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>17500</v>
+        <v>31700</v>
       </c>
       <c r="E41" s="3">
-        <v>25400</v>
+        <v>32400</v>
       </c>
       <c r="F41" s="3">
-        <v>34400</v>
+        <v>17700</v>
       </c>
       <c r="G41" s="3">
-        <v>19000</v>
+        <v>25600</v>
       </c>
       <c r="H41" s="3">
-        <v>28600</v>
+        <v>34700</v>
       </c>
       <c r="I41" s="3">
+        <v>19100</v>
+      </c>
+      <c r="J41" s="3">
+        <v>28800</v>
+      </c>
+      <c r="K41" s="3">
         <v>28200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>34100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>40400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>45500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>66400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>19200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>23300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>33600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>38700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>50400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>7100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>9300</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2905,68 +3078,74 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="D42" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>9900</v>
       </c>
-      <c r="H42" s="3">
-        <v>4600</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K42" s="3">
         <v>4500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>9000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>10300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>12300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>2600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>6900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>12500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>4400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>1900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>1200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>2800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>1300</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,68 +3158,74 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F43" s="3">
         <v>2300</v>
       </c>
-      <c r="E43" s="3">
-        <v>3400</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H43" s="3">
         <v>2800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>7600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>7400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>7900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>13600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>16300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>14200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>23200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>21200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>12200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>8800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>9400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>8100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>4400</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3053,68 +3238,74 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>9700</v>
+        <v>8300</v>
       </c>
       <c r="E44" s="3">
         <v>9100</v>
       </c>
       <c r="F44" s="3">
-        <v>10000</v>
+        <v>9800</v>
       </c>
       <c r="G44" s="3">
+        <v>9200</v>
+      </c>
+      <c r="H44" s="3">
+        <v>10100</v>
+      </c>
+      <c r="I44" s="3">
         <v>11000</v>
       </c>
-      <c r="H44" s="3">
-        <v>10900</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K44" s="3">
         <v>11800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>10800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>9400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>7700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>6200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>6600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>8400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>7100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>4600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>2900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>2400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1300</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3127,68 +3318,74 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>11300</v>
+        <v>3400</v>
       </c>
       <c r="E45" s="3">
-        <v>10500</v>
+        <v>11400</v>
       </c>
       <c r="F45" s="3">
-        <v>6200</v>
+        <v>11400</v>
       </c>
       <c r="G45" s="3">
-        <v>6700</v>
+        <v>10600</v>
       </c>
       <c r="H45" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I45" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J45" s="3">
         <v>4700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>6600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>4100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>4900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>4400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>3900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>3300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>3300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>3500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>3200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>4600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>3500</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3201,68 +3398,74 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>40800</v>
+        <v>63000</v>
       </c>
       <c r="E46" s="3">
-        <v>48500</v>
+        <v>59400</v>
       </c>
       <c r="F46" s="3">
-        <v>53500</v>
+        <v>41100</v>
       </c>
       <c r="G46" s="3">
-        <v>51900</v>
+        <v>48800</v>
       </c>
       <c r="H46" s="3">
-        <v>56500</v>
+        <v>53800</v>
       </c>
       <c r="I46" s="3">
+        <v>52300</v>
+      </c>
+      <c r="J46" s="3">
+        <v>56800</v>
+      </c>
+      <c r="K46" s="3">
         <v>58600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>65900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>78600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>86200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>93300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>59100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>68600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>60200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>57400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>67100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>25000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>19800</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,8 +3478,14 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3284,58 +3493,58 @@
         <v>3100</v>
       </c>
       <c r="E47" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F47" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G47" s="3">
         <v>2500</v>
       </c>
-      <c r="F47" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I47" s="3">
         <v>1400</v>
       </c>
-      <c r="H47" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K47" s="3">
         <v>1100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>2500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>2600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>7000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>7500</v>
-      </c>
-      <c r="R47" s="3">
-        <v>500</v>
-      </c>
-      <c r="S47" s="3">
-        <v>500</v>
       </c>
       <c r="T47" s="3">
         <v>500</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>500</v>
+      </c>
+      <c r="V47" s="3">
+        <v>500</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
@@ -3349,68 +3558,74 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F48" s="3">
+        <v>16300</v>
+      </c>
+      <c r="G48" s="3">
         <v>16200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
+        <v>16800</v>
+      </c>
+      <c r="I48" s="3">
         <v>16100</v>
       </c>
-      <c r="F48" s="3">
-        <v>16600</v>
-      </c>
-      <c r="G48" s="3">
-        <v>16000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>6900</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K48" s="3">
         <v>7300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>5000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2700</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3423,8 +3638,14 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3438,13 +3659,13 @@
         <v>300</v>
       </c>
       <c r="G49" s="3">
+        <v>300</v>
+      </c>
+      <c r="H49" s="3">
+        <v>300</v>
+      </c>
+      <c r="I49" s="3">
         <v>200</v>
-      </c>
-      <c r="H49" s="3">
-        <v>100</v>
-      </c>
-      <c r="I49" s="3">
-        <v>100</v>
       </c>
       <c r="J49" s="3">
         <v>100</v>
@@ -3462,10 +3683,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q49" s="3">
         <v>200</v>
@@ -3474,16 +3695,16 @@
         <v>200</v>
       </c>
       <c r="S49" s="3">
+        <v>200</v>
+      </c>
+      <c r="T49" s="3">
+        <v>200</v>
+      </c>
+      <c r="U49" s="3">
         <v>100</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
+      <c r="V49" s="3">
+        <v>0</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
@@ -3497,8 +3718,14 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3798,14 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,8 +3878,14 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3666,28 +3905,28 @@
         <v>200</v>
       </c>
       <c r="I52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K52" s="3">
         <v>300</v>
       </c>
       <c r="L52" s="3">
+        <v>300</v>
+      </c>
+      <c r="M52" s="3">
+        <v>300</v>
+      </c>
+      <c r="N52" s="3">
         <v>500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2800</v>
-      </c>
-      <c r="O52" s="3">
-        <v>100</v>
-      </c>
-      <c r="P52" s="3">
-        <v>100</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
@@ -3701,11 +3940,11 @@
       <c r="T52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
+      <c r="U52" s="3">
+        <v>100</v>
+      </c>
+      <c r="V52" s="3">
+        <v>100</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
@@ -3719,8 +3958,14 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,68 +4038,74 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>60600</v>
+        <v>83200</v>
       </c>
       <c r="E54" s="3">
-        <v>67500</v>
+        <v>80200</v>
       </c>
       <c r="F54" s="3">
-        <v>73300</v>
+        <v>61000</v>
       </c>
       <c r="G54" s="3">
-        <v>69700</v>
+        <v>68000</v>
       </c>
       <c r="H54" s="3">
-        <v>65100</v>
+        <v>73800</v>
       </c>
       <c r="I54" s="3">
+        <v>70100</v>
+      </c>
+      <c r="J54" s="3">
+        <v>65600</v>
+      </c>
+      <c r="K54" s="3">
         <v>67400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>73900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>86500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>94000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>103100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>67400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>73200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>69500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>67400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>70400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>28000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>23000</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,8 +4118,14 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4152,10 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,68 +4182,70 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G57" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I57" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J57" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K57" s="3">
+        <v>5500</v>
+      </c>
+      <c r="L57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="M57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="N57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="O57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="P57" s="3">
+        <v>7400</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>7700</v>
+      </c>
+      <c r="R57" s="3">
+        <v>6000</v>
+      </c>
+      <c r="S57" s="3">
         <v>4600</v>
       </c>
-      <c r="E57" s="3">
-        <v>4400</v>
-      </c>
-      <c r="F57" s="3">
-        <v>4900</v>
-      </c>
-      <c r="G57" s="3">
-        <v>4800</v>
-      </c>
-      <c r="H57" s="3">
-        <v>5600</v>
-      </c>
-      <c r="I57" s="3">
-        <v>5500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>6300</v>
-      </c>
-      <c r="K57" s="3">
-        <v>6300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>5100</v>
-      </c>
-      <c r="M57" s="3">
-        <v>5100</v>
-      </c>
-      <c r="N57" s="3">
-        <v>7400</v>
-      </c>
-      <c r="O57" s="3">
-        <v>7700</v>
-      </c>
-      <c r="P57" s="3">
-        <v>6000</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>4600</v>
-      </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>4300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2600</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,68 +4258,74 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>8400</v>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E58" s="3">
-        <v>19400</v>
+        <v>6000</v>
       </c>
       <c r="F58" s="3">
-        <v>16700</v>
+        <v>8500</v>
       </c>
       <c r="G58" s="3">
+        <v>19500</v>
+      </c>
+      <c r="H58" s="3">
+        <v>16800</v>
+      </c>
+      <c r="I58" s="3">
         <v>7500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>4700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1400</v>
-      </c>
-      <c r="M58" s="3">
-        <v>2200</v>
-      </c>
-      <c r="N58" s="3">
-        <v>2100</v>
       </c>
       <c r="O58" s="3">
         <v>2200</v>
       </c>
       <c r="P58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="R58" s="3">
         <v>1500</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>800</v>
-      </c>
-      <c r="R58" s="3">
-        <v>800</v>
       </c>
       <c r="S58" s="3">
         <v>800</v>
       </c>
       <c r="T58" s="3">
+        <v>800</v>
+      </c>
+      <c r="U58" s="3">
+        <v>800</v>
+      </c>
+      <c r="V58" s="3">
         <v>1600</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4071,68 +4338,74 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F59" s="3">
+        <v>17600</v>
+      </c>
+      <c r="G59" s="3">
+        <v>17400</v>
+      </c>
+      <c r="H59" s="3">
         <v>17500</v>
       </c>
-      <c r="E59" s="3">
-        <v>17300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>17400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>13900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>13700</v>
-      </c>
       <c r="I59" s="3">
+        <v>14000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>13800</v>
+      </c>
+      <c r="K59" s="3">
         <v>11700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>10800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>9100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>11200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>10800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>12500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>12500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>7100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>7900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>9900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>6300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>5100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4145,68 +4418,74 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>30500</v>
+      <c r="D60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E60" s="3">
-        <v>41100</v>
+        <v>27600</v>
       </c>
       <c r="F60" s="3">
-        <v>39000</v>
+        <v>30700</v>
       </c>
       <c r="G60" s="3">
-        <v>26200</v>
+        <v>41400</v>
       </c>
       <c r="H60" s="3">
-        <v>23900</v>
+        <v>39300</v>
       </c>
       <c r="I60" s="3">
+        <v>26400</v>
+      </c>
+      <c r="J60" s="3">
+        <v>24100</v>
+      </c>
+      <c r="K60" s="3">
         <v>20700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>18800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>16900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>17700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>18100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>22000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>22500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>14600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>13300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>15000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>10500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>9300</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,68 +4498,74 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F61" s="3">
         <v>400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2900</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>4600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>4800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>5100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>5000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>300</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4293,37 +4578,43 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F62" s="3">
         <v>11200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>11000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
+        <v>11100</v>
+      </c>
+      <c r="I62" s="3">
         <v>11000</v>
       </c>
-      <c r="G62" s="3">
-        <v>10900</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>1200</v>
-      </c>
-      <c r="L62" s="3">
-        <v>1200</v>
       </c>
       <c r="M62" s="3">
         <v>1200</v>
@@ -4332,29 +4623,29 @@
         <v>1200</v>
       </c>
       <c r="O62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q62" s="3">
         <v>1300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>800</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4367,8 +4658,14 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4738,14 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4818,14 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,68 +4898,74 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>47700</v>
+      <c r="D66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E66" s="3">
-        <v>58200</v>
+        <v>46700</v>
       </c>
       <c r="F66" s="3">
-        <v>56100</v>
+        <v>48100</v>
       </c>
       <c r="G66" s="3">
-        <v>43300</v>
+        <v>58600</v>
       </c>
       <c r="H66" s="3">
-        <v>32600</v>
+        <v>56500</v>
       </c>
       <c r="I66" s="3">
+        <v>43600</v>
+      </c>
+      <c r="J66" s="3">
+        <v>32800</v>
+      </c>
+      <c r="K66" s="3">
         <v>29600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>28000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>26600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>27500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>28100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>29000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>30100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>26400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>19600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>21600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>16600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>10700</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4978,14 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +5012,10 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +5088,14 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5168,14 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4890,17 +5225,17 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>102400</v>
       </c>
-      <c r="T70" s="3">
+      <c r="V70" s="3">
         <v>100800</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -4913,8 +5248,14 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,68 +5328,74 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-222900</v>
+      <c r="D72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E72" s="3">
-        <v>-212400</v>
+        <v>-233700</v>
       </c>
       <c r="F72" s="3">
-        <v>-200100</v>
+        <v>-224400</v>
       </c>
       <c r="G72" s="3">
-        <v>-184900</v>
+        <v>-213900</v>
       </c>
       <c r="H72" s="3">
-        <v>-174400</v>
+        <v>-201500</v>
       </c>
       <c r="I72" s="3">
+        <v>-186200</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-175600</v>
+      </c>
+      <c r="K72" s="3">
         <v>-164300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-154800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-144400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-134100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-124800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-112300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-111700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-111600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-116600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-112600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-108400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-105100</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5061,8 +5408,14 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5488,14 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5568,14 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,68 +5648,74 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>12900</v>
+        <v>29700</v>
       </c>
       <c r="E76" s="3">
-        <v>9300</v>
+        <v>33500</v>
       </c>
       <c r="F76" s="3">
-        <v>17200</v>
+        <v>13000</v>
       </c>
       <c r="G76" s="3">
-        <v>26400</v>
+        <v>9400</v>
       </c>
       <c r="H76" s="3">
-        <v>32500</v>
+        <v>17300</v>
       </c>
       <c r="I76" s="3">
+        <v>26500</v>
+      </c>
+      <c r="J76" s="3">
+        <v>32700</v>
+      </c>
+      <c r="K76" s="3">
         <v>37800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>45900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>59900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>66500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>75100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>38500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>43100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>43100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>47800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>48800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-91000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-88500</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5357,8 +5728,14 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5808,179 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-10400</v>
+      <c r="D81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E81" s="3">
-        <v>-12000</v>
+        <v>-9300</v>
       </c>
       <c r="F81" s="3">
-        <v>-15200</v>
+        <v>-10500</v>
       </c>
       <c r="G81" s="3">
-        <v>-10500</v>
+        <v>-12100</v>
       </c>
       <c r="H81" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="J81" s="3">
         <v>-10200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-9500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-14600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-10200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-10600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-8900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-6800</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-6000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-3400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-4100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-4000</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,82 +6007,90 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>1100</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>500</v>
-      </c>
-      <c r="M83" s="3">
-        <v>200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>900</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
       </c>
       <c r="P83" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
         <v>500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>-600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>200</v>
-      </c>
-      <c r="S83" s="3">
-        <v>200</v>
-      </c>
-      <c r="T83" s="3">
-        <v>400</v>
       </c>
       <c r="U83" s="3">
         <v>200</v>
       </c>
       <c r="V83" s="3">
+        <v>400</v>
+      </c>
+      <c r="W83" s="3">
         <v>200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y83" s="3">
         <v>400</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +6163,14 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6243,14 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6323,14 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6403,14 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6483,94 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
       </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>-16800</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>-6100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-21100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-6200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>4200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>2300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-4700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-6100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-2900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-4100</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,8 +6597,10 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6176,10 +6617,10 @@
         <v>-7500</v>
       </c>
       <c r="H91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-1100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -6188,52 +6629,58 @@
         <v>-1100</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6753,14 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6833,94 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>-4600</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>-7000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>3300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-9200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-3800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-5900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>1300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>1200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>1300</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6947,10 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6556,8 +7023,14 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +7103,14 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +7183,14 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,226 +7263,250 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>36900</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>38900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>40000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>5900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>6500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-51700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>39600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>3800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>7300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>7200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>2100</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3">
         <v>14800</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3">
         <v>25600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>46300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-25300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-10400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-53100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>43100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-2100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>2700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-600</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
   <si>
     <t>EH</t>
   </si>
@@ -656,364 +656,377 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>7900</v>
+        <v>8500</v>
       </c>
       <c r="E8" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F8" s="3">
         <v>4000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5000</v>
-      </c>
-      <c r="W8" s="3">
-        <v>1600</v>
       </c>
       <c r="X8" s="3">
         <v>1600</v>
       </c>
       <c r="Y8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Z8" s="3">
         <v>5400</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E9" s="3">
         <v>2800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2100</v>
-      </c>
-      <c r="W9" s="3">
-        <v>700</v>
       </c>
       <c r="X9" s="3">
         <v>700</v>
       </c>
       <c r="Y9" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z9" s="3">
         <v>2500</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E10" s="3">
         <v>5100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1400</v>
       </c>
-      <c r="I10" s="3">
-        <v>800</v>
-      </c>
       <c r="J10" s="3">
+        <v>700</v>
+      </c>
+      <c r="K10" s="3">
         <v>1400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5200</v>
-      </c>
-      <c r="U10" s="3">
-        <v>2900</v>
       </c>
       <c r="V10" s="3">
         <v>2900</v>
       </c>
       <c r="W10" s="3">
-        <v>900</v>
+        <v>2900</v>
       </c>
       <c r="X10" s="3">
         <v>900</v>
       </c>
       <c r="Y10" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z10" s="3">
         <v>2900</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1042,88 +1055,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E12" s="3">
         <v>5300</v>
-      </c>
-      <c r="E12" s="3">
-        <v>5200</v>
       </c>
       <c r="F12" s="3">
         <v>5200</v>
       </c>
       <c r="G12" s="3">
+        <v>5200</v>
+      </c>
+      <c r="H12" s="3">
         <v>7500</v>
       </c>
-      <c r="H12" s="3">
-        <v>5200</v>
-      </c>
       <c r="I12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J12" s="3">
         <v>4300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2900</v>
-      </c>
-      <c r="R12" s="3">
-        <v>2600</v>
       </c>
       <c r="S12" s="3">
         <v>2600</v>
       </c>
       <c r="T12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="U12" s="3">
         <v>2400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3900</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1202,8 +1219,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1282,8 +1302,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1362,8 +1385,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1389,168 +1415,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>17600</v>
       </c>
       <c r="E17" s="3">
-        <v>13700</v>
+        <v>18200</v>
       </c>
       <c r="F17" s="3">
-        <v>11900</v>
+        <v>13600</v>
       </c>
       <c r="G17" s="3">
-        <v>13600</v>
+        <v>11800</v>
       </c>
       <c r="H17" s="3">
-        <v>15000</v>
+        <v>13500</v>
       </c>
       <c r="I17" s="3">
-        <v>11400</v>
+        <v>14900</v>
       </c>
       <c r="J17" s="3">
+        <v>11300</v>
+      </c>
+      <c r="K17" s="3">
         <v>12400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9000</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-9100</v>
       </c>
       <c r="E18" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-9700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="H18" s="3">
         <v>-10500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-12800</v>
-      </c>
       <c r="I18" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-10200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1579,88 +1612,92 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>500</v>
       </c>
       <c r="E20" s="3">
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
-      </c>
-      <c r="U20" s="3">
-        <v>100</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
       </c>
       <c r="W20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1688,59 +1725,62 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-13300</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-10000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1754,13 +1794,13 @@
         <v>100</v>
       </c>
       <c r="G22" s="3">
+        <v>100</v>
+      </c>
+      <c r="H22" s="3">
         <v>1800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>100</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -1796,7 +1836,7 @@
         <v>100</v>
       </c>
       <c r="U22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1810,8 +1850,8 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
@@ -1819,88 +1859,94 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10100</v>
       </c>
-      <c r="E23" s="3">
-        <v>-9300</v>
-      </c>
       <c r="F23" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="K23" s="3">
         <v>-10300</v>
       </c>
-      <c r="G23" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-15300</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="O23" s="3">
         <v>-10600</v>
       </c>
-      <c r="J23" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1953,11 +1999,11 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -1968,19 +2014,22 @@
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2059,168 +2108,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-8700</v>
       </c>
       <c r="E26" s="3">
-        <v>-9300</v>
+        <v>-10100</v>
       </c>
       <c r="F26" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="K26" s="3">
         <v>-10300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-15300</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="N26" s="3">
         <v>-10300</v>
       </c>
-      <c r="K26" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3200</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>-1600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-8700</v>
       </c>
       <c r="E27" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-9300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="J27" s="3">
         <v>-10500</v>
       </c>
-      <c r="G27" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-15300</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="O27" s="3">
         <v>-10600</v>
       </c>
-      <c r="J27" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-14600</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-2700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2299,8 +2357,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2379,8 +2440,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2459,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2539,168 +2606,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-500</v>
       </c>
       <c r="E32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-100</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
       </c>
       <c r="W32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>1200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-8700</v>
       </c>
       <c r="E33" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-9300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="J33" s="3">
         <v>-10500</v>
       </c>
-      <c r="G33" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-15300</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="O33" s="3">
         <v>-10600</v>
       </c>
-      <c r="J33" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-14600</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-2700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2779,173 +2855,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-8700</v>
       </c>
       <c r="E35" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-9300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="J35" s="3">
         <v>-10500</v>
       </c>
-      <c r="G35" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-15300</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="O35" s="3">
         <v>-10600</v>
       </c>
-      <c r="J35" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-14600</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-2700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2974,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3004,71 +3090,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>31700</v>
+        <v>34700</v>
       </c>
       <c r="E41" s="3">
-        <v>32400</v>
+        <v>31500</v>
       </c>
       <c r="F41" s="3">
-        <v>17700</v>
+        <v>32200</v>
       </c>
       <c r="G41" s="3">
-        <v>25600</v>
+        <v>17600</v>
       </c>
       <c r="H41" s="3">
-        <v>34700</v>
+        <v>25400</v>
       </c>
       <c r="I41" s="3">
-        <v>19100</v>
+        <v>34400</v>
       </c>
       <c r="J41" s="3">
+        <v>19000</v>
+      </c>
+      <c r="K41" s="3">
         <v>28800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>28200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>34100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>40400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>45500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>66400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>23300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>33600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>38700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>50400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9300</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3084,71 +3171,74 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>10000</v>
+        <v>10100</v>
       </c>
       <c r="E42" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F42" s="3">
         <v>4000</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
+      <c r="H42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>9900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>12300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>6900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>12500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1300</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3164,71 +3254,74 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4800</v>
       </c>
-      <c r="E43" s="3">
-        <v>2600</v>
-      </c>
       <c r="F43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G43" s="3">
         <v>2300</v>
       </c>
-      <c r="G43" s="3">
-        <v>3500</v>
-      </c>
       <c r="H43" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I43" s="3">
         <v>2800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>14200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>23200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>21200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4400</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3244,71 +3337,74 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>8300</v>
+        <v>8600</v>
       </c>
       <c r="E44" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F44" s="3">
+        <v>9000</v>
+      </c>
+      <c r="G44" s="3">
+        <v>9700</v>
+      </c>
+      <c r="H44" s="3">
         <v>9100</v>
       </c>
-      <c r="F44" s="3">
-        <v>9800</v>
-      </c>
-      <c r="G44" s="3">
-        <v>9200</v>
-      </c>
-      <c r="H44" s="3">
-        <v>10100</v>
-      </c>
       <c r="I44" s="3">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="J44" s="3">
         <v>11000</v>
       </c>
       <c r="K44" s="3">
+        <v>11000</v>
+      </c>
+      <c r="L44" s="3">
         <v>11800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1300</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3324,71 +3420,74 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3400</v>
+        <v>3700</v>
       </c>
       <c r="E45" s="3">
-        <v>11400</v>
+        <v>8100</v>
       </c>
       <c r="F45" s="3">
-        <v>11400</v>
+        <v>11300</v>
       </c>
       <c r="G45" s="3">
-        <v>10600</v>
+        <v>11300</v>
       </c>
       <c r="H45" s="3">
-        <v>6300</v>
+        <v>10500</v>
       </c>
       <c r="I45" s="3">
-        <v>6800</v>
+        <v>6200</v>
       </c>
       <c r="J45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K45" s="3">
         <v>4700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3900</v>
-      </c>
-      <c r="P45" s="3">
-        <v>3300</v>
       </c>
       <c r="Q45" s="3">
         <v>3300</v>
       </c>
       <c r="R45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="S45" s="3">
         <v>3000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3500</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3404,71 +3503,74 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>63000</v>
+        <v>60100</v>
       </c>
       <c r="E46" s="3">
-        <v>59400</v>
+        <v>62600</v>
       </c>
       <c r="F46" s="3">
-        <v>41100</v>
+        <v>59000</v>
       </c>
       <c r="G46" s="3">
-        <v>48800</v>
+        <v>40900</v>
       </c>
       <c r="H46" s="3">
-        <v>53800</v>
+        <v>48500</v>
       </c>
       <c r="I46" s="3">
-        <v>52300</v>
+        <v>53500</v>
       </c>
       <c r="J46" s="3">
+        <v>51900</v>
+      </c>
+      <c r="K46" s="3">
         <v>56800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>58600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>65900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>78600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>86200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>93300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>59100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>68600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>60200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>57400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>67100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>25000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>19800</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3484,61 +3586,64 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E47" s="3">
         <v>3100</v>
       </c>
-      <c r="E47" s="3">
-        <v>3300</v>
-      </c>
       <c r="F47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G47" s="3">
         <v>3100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2500</v>
       </c>
-      <c r="H47" s="3">
-        <v>2800</v>
-      </c>
       <c r="I47" s="3">
-        <v>1400</v>
+        <v>2700</v>
       </c>
       <c r="J47" s="3">
         <v>1400</v>
       </c>
       <c r="K47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L47" s="3">
         <v>1100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2400</v>
-      </c>
-      <c r="N47" s="3">
-        <v>2300</v>
       </c>
       <c r="O47" s="3">
         <v>2300</v>
       </c>
       <c r="P47" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Q47" s="3">
         <v>2500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7500</v>
-      </c>
-      <c r="T47" s="3">
-        <v>500</v>
       </c>
       <c r="U47" s="3">
         <v>500</v>
@@ -3546,8 +3651,8 @@
       <c r="V47" s="3">
         <v>500</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
+      <c r="W47" s="3">
+        <v>500</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
@@ -3564,71 +3669,74 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>16600</v>
+        <v>18800</v>
       </c>
       <c r="E48" s="3">
-        <v>17000</v>
+        <v>16500</v>
       </c>
       <c r="F48" s="3">
-        <v>16300</v>
+        <v>16900</v>
       </c>
       <c r="G48" s="3">
         <v>16200</v>
       </c>
       <c r="H48" s="3">
-        <v>16800</v>
+        <v>16100</v>
       </c>
       <c r="I48" s="3">
-        <v>16100</v>
+        <v>16700</v>
       </c>
       <c r="J48" s="3">
+        <v>16000</v>
+      </c>
+      <c r="K48" s="3">
         <v>7000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2300</v>
-      </c>
-      <c r="T48" s="3">
-        <v>2500</v>
       </c>
       <c r="U48" s="3">
         <v>2500</v>
       </c>
       <c r="V48" s="3">
+        <v>2500</v>
+      </c>
+      <c r="W48" s="3">
         <v>2700</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3644,13 +3752,16 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E49" s="3">
         <v>300</v>
@@ -3665,10 +3776,10 @@
         <v>300</v>
       </c>
       <c r="I49" s="3">
+        <v>300</v>
+      </c>
+      <c r="J49" s="3">
         <v>200</v>
-      </c>
-      <c r="J49" s="3">
-        <v>100</v>
       </c>
       <c r="K49" s="3">
         <v>100</v>
@@ -3689,7 +3800,7 @@
         <v>100</v>
       </c>
       <c r="Q49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R49" s="3">
         <v>200</v>
@@ -3701,13 +3812,13 @@
         <v>200</v>
       </c>
       <c r="U49" s="3">
+        <v>200</v>
+      </c>
+      <c r="V49" s="3">
         <v>100</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
-      </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
+      <c r="W49" s="3">
+        <v>0</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
@@ -3724,8 +3835,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3804,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3884,8 +4001,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3911,7 +4031,7 @@
         <v>200</v>
       </c>
       <c r="K52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L52" s="3">
         <v>300</v>
@@ -3920,16 +4040,16 @@
         <v>300</v>
       </c>
       <c r="N52" s="3">
+        <v>300</v>
+      </c>
+      <c r="O52" s="3">
         <v>500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2800</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>100</v>
       </c>
       <c r="R52" s="3">
         <v>100</v>
@@ -3946,8 +4066,8 @@
       <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
+      <c r="W52" s="3">
+        <v>100</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
@@ -3964,8 +4084,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4044,71 +4167,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>83200</v>
+        <v>81900</v>
       </c>
       <c r="E54" s="3">
-        <v>80200</v>
+        <v>82700</v>
       </c>
       <c r="F54" s="3">
-        <v>61000</v>
+        <v>79700</v>
       </c>
       <c r="G54" s="3">
-        <v>68000</v>
+        <v>60600</v>
       </c>
       <c r="H54" s="3">
-        <v>73800</v>
+        <v>67600</v>
       </c>
       <c r="I54" s="3">
-        <v>70100</v>
+        <v>73300</v>
       </c>
       <c r="J54" s="3">
+        <v>69700</v>
+      </c>
+      <c r="K54" s="3">
         <v>65600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>67400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>73900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>86500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>94000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>103100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>67400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>73200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>69500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>67400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>70400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>28000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>23000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4124,8 +4250,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4154,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4184,71 +4314,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>5800</v>
       </c>
       <c r="E57" s="3">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="F57" s="3">
         <v>4700</v>
       </c>
       <c r="G57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H57" s="3">
         <v>4400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5500</v>
-      </c>
-      <c r="L57" s="3">
-        <v>6300</v>
       </c>
       <c r="M57" s="3">
         <v>6300</v>
       </c>
       <c r="N57" s="3">
-        <v>5100</v>
+        <v>6300</v>
       </c>
       <c r="O57" s="3">
         <v>5100</v>
       </c>
       <c r="P57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="Q57" s="3">
         <v>7400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2600</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4264,58 +4395,61 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>6000</v>
       </c>
       <c r="E58" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F58" s="3">
         <v>6000</v>
       </c>
-      <c r="F58" s="3">
-        <v>8500</v>
-      </c>
       <c r="G58" s="3">
-        <v>19500</v>
+        <v>8400</v>
       </c>
       <c r="H58" s="3">
-        <v>16800</v>
+        <v>19400</v>
       </c>
       <c r="I58" s="3">
+        <v>16700</v>
+      </c>
+      <c r="J58" s="3">
         <v>7500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1800</v>
-      </c>
-      <c r="M58" s="3">
-        <v>1400</v>
       </c>
       <c r="N58" s="3">
         <v>1400</v>
       </c>
       <c r="O58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P58" s="3">
         <v>2200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1500</v>
-      </c>
-      <c r="S58" s="3">
-        <v>800</v>
       </c>
       <c r="T58" s="3">
         <v>800</v>
@@ -4324,11 +4458,11 @@
         <v>800</v>
       </c>
       <c r="V58" s="3">
+        <v>800</v>
+      </c>
+      <c r="W58" s="3">
         <v>1600</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4344,71 +4478,74 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>18700</v>
       </c>
       <c r="E59" s="3">
-        <v>17000</v>
+        <v>19600</v>
       </c>
       <c r="F59" s="3">
-        <v>17600</v>
+        <v>16900</v>
       </c>
       <c r="G59" s="3">
+        <v>17500</v>
+      </c>
+      <c r="H59" s="3">
+        <v>17300</v>
+      </c>
+      <c r="I59" s="3">
         <v>17400</v>
       </c>
-      <c r="H59" s="3">
-        <v>17500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>14000</v>
-      </c>
       <c r="J59" s="3">
+        <v>13900</v>
+      </c>
+      <c r="K59" s="3">
         <v>13800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10800</v>
-      </c>
-      <c r="P59" s="3">
-        <v>12500</v>
       </c>
       <c r="Q59" s="3">
         <v>12500</v>
       </c>
       <c r="R59" s="3">
+        <v>12500</v>
+      </c>
+      <c r="S59" s="3">
         <v>7100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4424,71 +4561,74 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>3</v>
+      <c r="D60" s="3">
+        <v>30500</v>
       </c>
       <c r="E60" s="3">
-        <v>27600</v>
+        <v>34600</v>
       </c>
       <c r="F60" s="3">
-        <v>30700</v>
+        <v>27500</v>
       </c>
       <c r="G60" s="3">
-        <v>41400</v>
+        <v>30500</v>
       </c>
       <c r="H60" s="3">
-        <v>39300</v>
+        <v>41100</v>
       </c>
       <c r="I60" s="3">
-        <v>26400</v>
+        <v>39000</v>
       </c>
       <c r="J60" s="3">
+        <v>26200</v>
+      </c>
+      <c r="K60" s="3">
         <v>24100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>15000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9300</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4504,71 +4644,74 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E61" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F61" s="3">
         <v>1500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>400</v>
-      </c>
-      <c r="G61" s="3">
-        <v>500</v>
       </c>
       <c r="H61" s="3">
         <v>500</v>
       </c>
       <c r="I61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J61" s="3">
         <v>600</v>
       </c>
       <c r="K61" s="3">
+        <v>600</v>
+      </c>
+      <c r="L61" s="3">
         <v>700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2300</v>
-      </c>
-      <c r="M61" s="3">
-        <v>2800</v>
       </c>
       <c r="N61" s="3">
         <v>2800</v>
       </c>
       <c r="O61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="P61" s="3">
         <v>2900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>4600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>300</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4584,40 +4727,43 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>14300</v>
       </c>
       <c r="E62" s="3">
-        <v>12000</v>
+        <v>11700</v>
       </c>
       <c r="F62" s="3">
+        <v>11900</v>
+      </c>
+      <c r="G62" s="3">
         <v>11200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11100</v>
       </c>
-      <c r="I62" s="3">
-        <v>11000</v>
-      </c>
       <c r="J62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K62" s="3">
         <v>2400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>1200</v>
       </c>
       <c r="N62" s="3">
         <v>1200</v>
@@ -4629,25 +4775,25 @@
         <v>1200</v>
       </c>
       <c r="Q62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R62" s="3">
         <v>1300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>800</v>
-      </c>
-      <c r="S62" s="3">
-        <v>900</v>
       </c>
       <c r="T62" s="3">
         <v>900</v>
       </c>
       <c r="U62" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="V62" s="3">
         <v>800</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
+      <c r="W62" s="3">
+        <v>800</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
@@ -4664,8 +4810,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4744,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4824,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4904,71 +5059,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>3</v>
+      <c r="D66" s="3">
+        <v>52500</v>
       </c>
       <c r="E66" s="3">
-        <v>46700</v>
+        <v>53200</v>
       </c>
       <c r="F66" s="3">
-        <v>48100</v>
+        <v>46500</v>
       </c>
       <c r="G66" s="3">
-        <v>58600</v>
+        <v>47800</v>
       </c>
       <c r="H66" s="3">
-        <v>56500</v>
+        <v>58200</v>
       </c>
       <c r="I66" s="3">
-        <v>43600</v>
+        <v>56200</v>
       </c>
       <c r="J66" s="3">
+        <v>43300</v>
+      </c>
+      <c r="K66" s="3">
         <v>32800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>29600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>30100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>26400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>21600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10700</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,8 +5142,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5014,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5094,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5174,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5231,14 +5399,14 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>102400</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>100800</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5254,8 +5422,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5334,71 +5505,74 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>-251000</v>
       </c>
       <c r="E72" s="3">
-        <v>-233700</v>
+        <v>-242200</v>
       </c>
       <c r="F72" s="3">
-        <v>-224400</v>
+        <v>-232300</v>
       </c>
       <c r="G72" s="3">
-        <v>-213900</v>
+        <v>-223000</v>
       </c>
       <c r="H72" s="3">
-        <v>-201500</v>
+        <v>-212500</v>
       </c>
       <c r="I72" s="3">
-        <v>-186200</v>
+        <v>-200200</v>
       </c>
       <c r="J72" s="3">
+        <v>-185000</v>
+      </c>
+      <c r="K72" s="3">
         <v>-175600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-164300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-154800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-144400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-134100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-124800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-112300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-111700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-111600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-116600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-112600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-108400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-105100</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5414,8 +5588,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5494,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5574,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5654,71 +5837,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>29700</v>
+        <v>29400</v>
       </c>
       <c r="E76" s="3">
-        <v>33500</v>
+        <v>29500</v>
       </c>
       <c r="F76" s="3">
-        <v>13000</v>
+        <v>33200</v>
       </c>
       <c r="G76" s="3">
-        <v>9400</v>
+        <v>12900</v>
       </c>
       <c r="H76" s="3">
-        <v>17300</v>
+        <v>9300</v>
       </c>
       <c r="I76" s="3">
-        <v>26500</v>
+        <v>17200</v>
       </c>
       <c r="J76" s="3">
+        <v>26400</v>
+      </c>
+      <c r="K76" s="3">
         <v>32700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>37800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>59900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>66500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>75100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>38500</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>43100</v>
       </c>
       <c r="R76" s="3">
         <v>43100</v>
       </c>
       <c r="S76" s="3">
+        <v>43100</v>
+      </c>
+      <c r="T76" s="3">
         <v>47800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>48800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-91000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-88500</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5734,8 +5920,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5814,173 +6003,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-8700</v>
       </c>
       <c r="E81" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-9300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="J81" s="3">
         <v>-10500</v>
       </c>
-      <c r="G81" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-15300</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="O81" s="3">
         <v>-10600</v>
       </c>
-      <c r="J81" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-14600</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-2700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6009,8 +6207,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6035,62 +6234,65 @@
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
         <v>1100</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>-600</v>
-      </c>
-      <c r="T83" s="3">
-        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>200</v>
       </c>
       <c r="V83" s="3">
+        <v>200</v>
+      </c>
+      <c r="W83" s="3">
         <v>400</v>
-      </c>
-      <c r="W83" s="3">
-        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
       </c>
       <c r="Y83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z83" s="3">
         <v>400</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6169,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6249,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6329,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6409,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6489,8 +6703,11 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6515,62 +6732,65 @@
       <c r="J89" s="3">
         <v>0</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>-16800</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>-6100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6599,8 +6819,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6614,7 +6835,7 @@
         <v>-8300</v>
       </c>
       <c r="G91" s="3">
-        <v>-7500</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -6626,52 +6847,52 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-1200</v>
       </c>
       <c r="P91" s="3">
         <v>-1200</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W91" s="3">
         <v>-100</v>
       </c>
       <c r="X91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
+      <c r="Z91" s="3">
+        <v>-400</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
@@ -6679,8 +6900,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6759,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6839,8 +7066,11 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6865,62 +7095,65 @@
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
         <v>-4600</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>-7000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1300</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6949,8 +7182,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7029,8 +7263,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7109,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7189,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7269,8 +7512,11 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7295,62 +7541,65 @@
       <c r="J100" s="3">
         <v>0</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>36900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>38900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>40000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-51700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>39600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>7300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>7200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2100</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7375,62 +7624,65 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
         <v>-700</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7455,58 +7707,61 @@
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3">
         <v>14800</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>25600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>46300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-25300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-53100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>43100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-600</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
   <si>
     <t>EH</t>
   </si>
@@ -656,377 +656,390 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>8500</v>
+        <v>14400</v>
       </c>
       <c r="E8" s="3">
-        <v>7800</v>
+        <v>8700</v>
       </c>
       <c r="F8" s="3">
+        <v>8000</v>
+      </c>
+      <c r="G8" s="3">
         <v>4000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5000</v>
-      </c>
-      <c r="X8" s="3">
-        <v>1600</v>
       </c>
       <c r="Y8" s="3">
         <v>1600</v>
       </c>
       <c r="Z8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AA8" s="3">
         <v>5400</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E9" s="3">
         <v>3300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2100</v>
-      </c>
-      <c r="X9" s="3">
-        <v>700</v>
       </c>
       <c r="Y9" s="3">
         <v>700</v>
       </c>
       <c r="Z9" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA9" s="3">
         <v>2500</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>5300</v>
+        <v>9000</v>
       </c>
       <c r="E10" s="3">
-        <v>5100</v>
+        <v>5400</v>
       </c>
       <c r="F10" s="3">
+        <v>5200</v>
+      </c>
+      <c r="G10" s="3">
         <v>2600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K10" s="3">
+        <v>700</v>
+      </c>
+      <c r="L10" s="3">
         <v>1400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="M10" s="3">
+        <v>500</v>
+      </c>
+      <c r="N10" s="3">
         <v>700</v>
       </c>
-      <c r="K10" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L10" s="3">
-        <v>500</v>
-      </c>
-      <c r="M10" s="3">
-        <v>700</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5200</v>
-      </c>
-      <c r="V10" s="3">
-        <v>2900</v>
       </c>
       <c r="W10" s="3">
         <v>2900</v>
       </c>
       <c r="X10" s="3">
-        <v>900</v>
+        <v>2900</v>
       </c>
       <c r="Y10" s="3">
         <v>900</v>
       </c>
       <c r="Z10" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA10" s="3">
         <v>2900</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,91 +1069,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>5200</v>
+        <v>8700</v>
       </c>
       <c r="E12" s="3">
         <v>5300</v>
       </c>
       <c r="F12" s="3">
+        <v>5400</v>
+      </c>
+      <c r="G12" s="3">
+        <v>5300</v>
+      </c>
+      <c r="H12" s="3">
+        <v>5300</v>
+      </c>
+      <c r="I12" s="3">
+        <v>7600</v>
+      </c>
+      <c r="J12" s="3">
         <v>5200</v>
       </c>
-      <c r="G12" s="3">
-        <v>5200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>7500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>5100</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2900</v>
-      </c>
-      <c r="S12" s="3">
-        <v>2600</v>
       </c>
       <c r="T12" s="3">
         <v>2600</v>
       </c>
       <c r="U12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="V12" s="3">
         <v>2400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3900</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1222,8 +1239,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1305,8 +1325,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1388,8 +1411,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17600</v>
+        <v>25300</v>
       </c>
       <c r="E17" s="3">
-        <v>18200</v>
+        <v>18000</v>
       </c>
       <c r="F17" s="3">
-        <v>13600</v>
+        <v>18600</v>
       </c>
       <c r="G17" s="3">
-        <v>11800</v>
+        <v>13900</v>
       </c>
       <c r="H17" s="3">
-        <v>13500</v>
+        <v>12000</v>
       </c>
       <c r="I17" s="3">
-        <v>14900</v>
+        <v>13800</v>
       </c>
       <c r="J17" s="3">
+        <v>15200</v>
+      </c>
+      <c r="K17" s="3">
         <v>11300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9000</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-9100</v>
+        <v>-10900</v>
       </c>
       <c r="E18" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="O18" s="3">
         <v>-10400</v>
       </c>
-      <c r="F18" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-10400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-12700</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-14600</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-10400</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-10600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,91 +1646,95 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-200</v>
-      </c>
-      <c r="V20" s="3">
-        <v>100</v>
       </c>
       <c r="W20" s="3">
         <v>100</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1728,59 +1765,62 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-13300</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-10000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-5300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1797,13 +1837,13 @@
         <v>100</v>
       </c>
       <c r="H22" s="3">
+        <v>100</v>
+      </c>
+      <c r="I22" s="3">
         <v>1800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
@@ -1839,7 +1879,7 @@
         <v>100</v>
       </c>
       <c r="V22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1853,8 +1893,8 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
@@ -1862,91 +1902,97 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-8700</v>
+        <v>-10000</v>
       </c>
       <c r="E23" s="3">
-        <v>-10100</v>
+        <v>-8900</v>
       </c>
       <c r="F23" s="3">
-        <v>-9200</v>
+        <v>-10300</v>
       </c>
       <c r="G23" s="3">
-        <v>-10200</v>
+        <v>-9400</v>
       </c>
       <c r="H23" s="3">
-        <v>-12000</v>
+        <v>-10400</v>
       </c>
       <c r="I23" s="3">
-        <v>-15200</v>
+        <v>-12300</v>
       </c>
       <c r="J23" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="K23" s="3">
         <v>-10600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2002,11 +2048,11 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
@@ -2017,19 +2063,22 @@
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-8700</v>
+        <v>-10000</v>
       </c>
       <c r="E26" s="3">
-        <v>-10100</v>
+        <v>-8900</v>
       </c>
       <c r="F26" s="3">
-        <v>-9200</v>
+        <v>-10300</v>
       </c>
       <c r="G26" s="3">
-        <v>-10200</v>
+        <v>-9400</v>
       </c>
       <c r="H26" s="3">
-        <v>-12000</v>
+        <v>-10400</v>
       </c>
       <c r="I26" s="3">
-        <v>-15200</v>
+        <v>-12300</v>
       </c>
       <c r="J26" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="K26" s="3">
         <v>-10600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3200</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>-1600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-8700</v>
+        <v>-10100</v>
       </c>
       <c r="E27" s="3">
-        <v>-10000</v>
+        <v>-8900</v>
       </c>
       <c r="F27" s="3">
-        <v>-9300</v>
+        <v>-10200</v>
       </c>
       <c r="G27" s="3">
-        <v>-10400</v>
+        <v>-9500</v>
       </c>
       <c r="H27" s="3">
-        <v>-12000</v>
+        <v>-10700</v>
       </c>
       <c r="I27" s="3">
-        <v>-15200</v>
+        <v>-12200</v>
       </c>
       <c r="J27" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="K27" s="3">
         <v>-10500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6800</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>-2700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2443,8 +2504,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,174 +2676,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>200</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-100</v>
       </c>
       <c r="W32" s="3">
         <v>-100</v>
       </c>
       <c r="X32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-8700</v>
+        <v>-10100</v>
       </c>
       <c r="E33" s="3">
-        <v>-10000</v>
+        <v>-8900</v>
       </c>
       <c r="F33" s="3">
-        <v>-9300</v>
+        <v>-10200</v>
       </c>
       <c r="G33" s="3">
-        <v>-10400</v>
+        <v>-9500</v>
       </c>
       <c r="H33" s="3">
-        <v>-12000</v>
+        <v>-10700</v>
       </c>
       <c r="I33" s="3">
-        <v>-15200</v>
+        <v>-12200</v>
       </c>
       <c r="J33" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="K33" s="3">
         <v>-10500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6800</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>-2700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-8700</v>
+        <v>-10100</v>
       </c>
       <c r="E35" s="3">
-        <v>-10000</v>
+        <v>-8900</v>
       </c>
       <c r="F35" s="3">
-        <v>-9300</v>
+        <v>-10200</v>
       </c>
       <c r="G35" s="3">
-        <v>-10400</v>
+        <v>-9500</v>
       </c>
       <c r="H35" s="3">
-        <v>-12000</v>
+        <v>-10700</v>
       </c>
       <c r="I35" s="3">
-        <v>-15200</v>
+        <v>-12200</v>
       </c>
       <c r="J35" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="K35" s="3">
         <v>-10500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6800</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>-2700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,74 +3177,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>34700</v>
+        <v>87900</v>
       </c>
       <c r="E41" s="3">
-        <v>31500</v>
+        <v>35400</v>
       </c>
       <c r="F41" s="3">
         <v>32200</v>
       </c>
       <c r="G41" s="3">
-        <v>17600</v>
+        <v>32900</v>
       </c>
       <c r="H41" s="3">
-        <v>25400</v>
+        <v>17900</v>
       </c>
       <c r="I41" s="3">
-        <v>34400</v>
+        <v>26000</v>
       </c>
       <c r="J41" s="3">
+        <v>35100</v>
+      </c>
+      <c r="K41" s="3">
         <v>19000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>28800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>28200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>34100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>40400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>45500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>66400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>23300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>33600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>38700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>50400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9300</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,74 +3261,77 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F42" s="3">
         <v>10100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>9900</v>
       </c>
-      <c r="F42" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>9900</v>
-      </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>10300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>12300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>6900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>12500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1300</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3257,74 +3347,77 @@
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3000</v>
+        <v>6900</v>
       </c>
       <c r="E43" s="3">
-        <v>4800</v>
+        <v>3100</v>
       </c>
       <c r="F43" s="3">
-        <v>2500</v>
+        <v>4900</v>
       </c>
       <c r="G43" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H43" s="3">
         <v>2300</v>
       </c>
-      <c r="H43" s="3">
-        <v>3400</v>
-      </c>
       <c r="I43" s="3">
-        <v>2800</v>
+        <v>3500</v>
       </c>
       <c r="J43" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K43" s="3">
         <v>5400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>14200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>23200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>21200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4400</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3340,74 +3433,77 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>8600</v>
+        <v>10000</v>
       </c>
       <c r="E44" s="3">
-        <v>8200</v>
+        <v>8800</v>
       </c>
       <c r="F44" s="3">
-        <v>9000</v>
+        <v>8400</v>
       </c>
       <c r="G44" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="H44" s="3">
-        <v>9100</v>
+        <v>9900</v>
       </c>
       <c r="I44" s="3">
-        <v>10000</v>
+        <v>9300</v>
       </c>
       <c r="J44" s="3">
-        <v>11000</v>
+        <v>10200</v>
       </c>
       <c r="K44" s="3">
         <v>11000</v>
       </c>
       <c r="L44" s="3">
+        <v>11000</v>
+      </c>
+      <c r="M44" s="3">
         <v>11800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>9400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1300</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3423,74 +3519,77 @@
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3700</v>
+        <v>7400</v>
       </c>
       <c r="E45" s="3">
-        <v>8100</v>
+        <v>3800</v>
       </c>
       <c r="F45" s="3">
-        <v>11300</v>
+        <v>8300</v>
       </c>
       <c r="G45" s="3">
-        <v>11300</v>
+        <v>11500</v>
       </c>
       <c r="H45" s="3">
-        <v>10500</v>
+        <v>11500</v>
       </c>
       <c r="I45" s="3">
-        <v>6200</v>
+        <v>10700</v>
       </c>
       <c r="J45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="K45" s="3">
         <v>6700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3900</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>3300</v>
       </c>
       <c r="R45" s="3">
         <v>3300</v>
       </c>
       <c r="S45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T45" s="3">
         <v>3000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3500</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,74 +3605,77 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>60100</v>
+        <v>159300</v>
       </c>
       <c r="E46" s="3">
-        <v>62600</v>
+        <v>61300</v>
       </c>
       <c r="F46" s="3">
-        <v>59000</v>
+        <v>63900</v>
       </c>
       <c r="G46" s="3">
-        <v>40900</v>
+        <v>60200</v>
       </c>
       <c r="H46" s="3">
-        <v>48500</v>
+        <v>41700</v>
       </c>
       <c r="I46" s="3">
-        <v>53500</v>
+        <v>49500</v>
       </c>
       <c r="J46" s="3">
+        <v>54600</v>
+      </c>
+      <c r="K46" s="3">
         <v>51900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>56800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>58600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>65900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>78600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>86200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>93300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>59100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>68600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>60200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>57400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>67100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>25000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19800</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3589,8 +3691,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3598,55 +3703,55 @@
         <v>2500</v>
       </c>
       <c r="E47" s="3">
-        <v>3100</v>
+        <v>2500</v>
       </c>
       <c r="F47" s="3">
         <v>3200</v>
       </c>
       <c r="G47" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H47" s="3">
         <v>3100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2500</v>
       </c>
-      <c r="I47" s="3">
-        <v>2700</v>
-      </c>
       <c r="J47" s="3">
-        <v>1400</v>
+        <v>2800</v>
       </c>
       <c r="K47" s="3">
         <v>1400</v>
       </c>
       <c r="L47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M47" s="3">
         <v>1100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2400</v>
-      </c>
-      <c r="O47" s="3">
-        <v>2300</v>
       </c>
       <c r="P47" s="3">
         <v>2300</v>
       </c>
       <c r="Q47" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R47" s="3">
         <v>2500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7500</v>
-      </c>
-      <c r="U47" s="3">
-        <v>500</v>
       </c>
       <c r="V47" s="3">
         <v>500</v>
@@ -3654,8 +3759,8 @@
       <c r="W47" s="3">
         <v>500</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
+      <c r="X47" s="3">
+        <v>500</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
@@ -3672,74 +3777,77 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>18800</v>
+        <v>22900</v>
       </c>
       <c r="E48" s="3">
+        <v>19200</v>
+      </c>
+      <c r="F48" s="3">
+        <v>16800</v>
+      </c>
+      <c r="G48" s="3">
+        <v>17200</v>
+      </c>
+      <c r="H48" s="3">
         <v>16500</v>
       </c>
-      <c r="F48" s="3">
-        <v>16900</v>
-      </c>
-      <c r="G48" s="3">
-        <v>16200</v>
-      </c>
-      <c r="H48" s="3">
-        <v>16100</v>
-      </c>
       <c r="I48" s="3">
-        <v>16700</v>
+        <v>16400</v>
       </c>
       <c r="J48" s="3">
+        <v>17000</v>
+      </c>
+      <c r="K48" s="3">
         <v>16000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2300</v>
-      </c>
-      <c r="U48" s="3">
-        <v>2500</v>
       </c>
       <c r="V48" s="3">
         <v>2500</v>
       </c>
       <c r="W48" s="3">
+        <v>2500</v>
+      </c>
+      <c r="X48" s="3">
         <v>2700</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3755,16 +3863,19 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>300</v>
+      </c>
+      <c r="E49" s="3">
         <v>400</v>
-      </c>
-      <c r="E49" s="3">
-        <v>300</v>
       </c>
       <c r="F49" s="3">
         <v>300</v>
@@ -3779,10 +3890,10 @@
         <v>300</v>
       </c>
       <c r="J49" s="3">
+        <v>300</v>
+      </c>
+      <c r="K49" s="3">
         <v>200</v>
-      </c>
-      <c r="K49" s="3">
-        <v>100</v>
       </c>
       <c r="L49" s="3">
         <v>100</v>
@@ -3803,7 +3914,7 @@
         <v>100</v>
       </c>
       <c r="R49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S49" s="3">
         <v>200</v>
@@ -3815,13 +3926,13 @@
         <v>200</v>
       </c>
       <c r="V49" s="3">
+        <v>200</v>
+      </c>
+      <c r="W49" s="3">
         <v>100</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
+      <c r="X49" s="3">
+        <v>0</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
@@ -3838,8 +3949,11 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,13 +4121,16 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
@@ -4034,7 +4154,7 @@
         <v>200</v>
       </c>
       <c r="L52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M52" s="3">
         <v>300</v>
@@ -4043,16 +4163,16 @@
         <v>300</v>
       </c>
       <c r="O52" s="3">
+        <v>300</v>
+      </c>
+      <c r="P52" s="3">
         <v>500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2800</v>
-      </c>
-      <c r="R52" s="3">
-        <v>100</v>
       </c>
       <c r="S52" s="3">
         <v>100</v>
@@ -4069,8 +4189,8 @@
       <c r="W52" s="3">
         <v>100</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
+      <c r="X52" s="3">
+        <v>100</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
@@ -4087,8 +4207,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,74 +4293,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>81900</v>
+        <v>185300</v>
       </c>
       <c r="E54" s="3">
-        <v>82700</v>
+        <v>83600</v>
       </c>
       <c r="F54" s="3">
-        <v>79700</v>
+        <v>84400</v>
       </c>
       <c r="G54" s="3">
-        <v>60600</v>
+        <v>81300</v>
       </c>
       <c r="H54" s="3">
-        <v>67600</v>
+        <v>61900</v>
       </c>
       <c r="I54" s="3">
-        <v>73300</v>
+        <v>69000</v>
       </c>
       <c r="J54" s="3">
+        <v>74800</v>
+      </c>
+      <c r="K54" s="3">
         <v>69700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>65600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>67400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>73900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>86500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>94000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>103100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>67400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>73200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>69500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>67400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>70400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>28000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23000</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4253,8 +4379,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,74 +4445,75 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5800</v>
+        <v>10400</v>
       </c>
       <c r="E57" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="I57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="J57" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K57" s="3">
         <v>4800</v>
       </c>
-      <c r="F57" s="3">
-        <v>4700</v>
-      </c>
-      <c r="G57" s="3">
-        <v>4600</v>
-      </c>
-      <c r="H57" s="3">
-        <v>4400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J57" s="3">
-        <v>4800</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5500</v>
-      </c>
-      <c r="M57" s="3">
-        <v>6300</v>
       </c>
       <c r="N57" s="3">
         <v>6300</v>
       </c>
       <c r="O57" s="3">
-        <v>5100</v>
+        <v>6300</v>
       </c>
       <c r="P57" s="3">
         <v>5100</v>
       </c>
       <c r="Q57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="R57" s="3">
         <v>7400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2600</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4398,61 +4529,64 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6000</v>
+        <v>23000</v>
       </c>
       <c r="E58" s="3">
-        <v>10100</v>
+        <v>6100</v>
       </c>
       <c r="F58" s="3">
-        <v>6000</v>
+        <v>10300</v>
       </c>
       <c r="G58" s="3">
-        <v>8400</v>
+        <v>6100</v>
       </c>
       <c r="H58" s="3">
-        <v>19400</v>
+        <v>8600</v>
       </c>
       <c r="I58" s="3">
-        <v>16700</v>
+        <v>19800</v>
       </c>
       <c r="J58" s="3">
+        <v>17000</v>
+      </c>
+      <c r="K58" s="3">
         <v>7500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1800</v>
-      </c>
-      <c r="N58" s="3">
-        <v>1400</v>
       </c>
       <c r="O58" s="3">
         <v>1400</v>
       </c>
       <c r="P58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q58" s="3">
         <v>2200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1500</v>
-      </c>
-      <c r="T58" s="3">
-        <v>800</v>
       </c>
       <c r="U58" s="3">
         <v>800</v>
@@ -4461,11 +4595,11 @@
         <v>800</v>
       </c>
       <c r="W58" s="3">
+        <v>800</v>
+      </c>
+      <c r="X58" s="3">
         <v>1600</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4481,74 +4615,77 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>18700</v>
+        <v>41500</v>
       </c>
       <c r="E59" s="3">
-        <v>19600</v>
+        <v>19100</v>
       </c>
       <c r="F59" s="3">
-        <v>16900</v>
+        <v>20000</v>
       </c>
       <c r="G59" s="3">
-        <v>17500</v>
+        <v>17200</v>
       </c>
       <c r="H59" s="3">
-        <v>17300</v>
+        <v>17800</v>
       </c>
       <c r="I59" s="3">
-        <v>17400</v>
+        <v>17700</v>
       </c>
       <c r="J59" s="3">
+        <v>17800</v>
+      </c>
+      <c r="K59" s="3">
         <v>13900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10800</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>12500</v>
       </c>
       <c r="R59" s="3">
         <v>12500</v>
       </c>
       <c r="S59" s="3">
+        <v>12500</v>
+      </c>
+      <c r="T59" s="3">
         <v>7100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4564,74 +4701,77 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>30500</v>
+        <v>75000</v>
       </c>
       <c r="E60" s="3">
-        <v>34600</v>
+        <v>31100</v>
       </c>
       <c r="F60" s="3">
-        <v>27500</v>
+        <v>35300</v>
       </c>
       <c r="G60" s="3">
-        <v>30500</v>
+        <v>28000</v>
       </c>
       <c r="H60" s="3">
-        <v>41100</v>
+        <v>31200</v>
       </c>
       <c r="I60" s="3">
-        <v>39000</v>
+        <v>42000</v>
       </c>
       <c r="J60" s="3">
+        <v>39800</v>
+      </c>
+      <c r="K60" s="3">
         <v>26200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>24100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>15000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9300</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4647,74 +4787,77 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="E61" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F61" s="3">
         <v>1300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>400</v>
-      </c>
-      <c r="H61" s="3">
-        <v>500</v>
       </c>
       <c r="I61" s="3">
         <v>500</v>
       </c>
       <c r="J61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K61" s="3">
         <v>600</v>
       </c>
       <c r="L61" s="3">
+        <v>600</v>
+      </c>
+      <c r="M61" s="3">
         <v>700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2300</v>
-      </c>
-      <c r="N61" s="3">
-        <v>2800</v>
       </c>
       <c r="O61" s="3">
         <v>2800</v>
       </c>
       <c r="P61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Q61" s="3">
         <v>2900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>4600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>300</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4730,43 +4873,46 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>14300</v>
+        <v>18300</v>
       </c>
       <c r="E62" s="3">
-        <v>11700</v>
+        <v>14600</v>
       </c>
       <c r="F62" s="3">
-        <v>11900</v>
+        <v>12000</v>
       </c>
       <c r="G62" s="3">
+        <v>12100</v>
+      </c>
+      <c r="H62" s="3">
+        <v>11400</v>
+      </c>
+      <c r="I62" s="3">
         <v>11200</v>
       </c>
-      <c r="H62" s="3">
-        <v>11000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>11100</v>
-      </c>
       <c r="J62" s="3">
+        <v>11300</v>
+      </c>
+      <c r="K62" s="3">
         <v>10900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1100</v>
-      </c>
-      <c r="N62" s="3">
-        <v>1200</v>
       </c>
       <c r="O62" s="3">
         <v>1200</v>
@@ -4778,25 +4924,25 @@
         <v>1200</v>
       </c>
       <c r="R62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S62" s="3">
         <v>1300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>800</v>
-      </c>
-      <c r="T62" s="3">
-        <v>900</v>
       </c>
       <c r="U62" s="3">
         <v>900</v>
       </c>
       <c r="V62" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="W62" s="3">
         <v>800</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
+      <c r="X62" s="3">
+        <v>800</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
@@ -4813,8 +4959,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,74 +5217,77 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>52500</v>
+        <v>95200</v>
       </c>
       <c r="E66" s="3">
-        <v>53200</v>
+        <v>53600</v>
       </c>
       <c r="F66" s="3">
-        <v>46500</v>
+        <v>54300</v>
       </c>
       <c r="G66" s="3">
-        <v>47800</v>
+        <v>47400</v>
       </c>
       <c r="H66" s="3">
-        <v>58200</v>
+        <v>48700</v>
       </c>
       <c r="I66" s="3">
-        <v>56200</v>
+        <v>59400</v>
       </c>
       <c r="J66" s="3">
+        <v>57300</v>
+      </c>
+      <c r="K66" s="3">
         <v>43300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>29600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>27500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>30100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>26400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>21600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10700</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5145,8 +5303,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5402,14 +5570,14 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>102400</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>100800</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5425,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,74 +5679,77 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-251000</v>
+        <v>-266200</v>
       </c>
       <c r="E72" s="3">
-        <v>-242200</v>
+        <v>-256100</v>
       </c>
       <c r="F72" s="3">
-        <v>-232300</v>
+        <v>-247200</v>
       </c>
       <c r="G72" s="3">
-        <v>-223000</v>
+        <v>-237000</v>
       </c>
       <c r="H72" s="3">
-        <v>-212500</v>
+        <v>-227500</v>
       </c>
       <c r="I72" s="3">
-        <v>-200200</v>
+        <v>-216900</v>
       </c>
       <c r="J72" s="3">
+        <v>-204300</v>
+      </c>
+      <c r="K72" s="3">
         <v>-185000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-175600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-164300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-154800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-144400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-134100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-124800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-112300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-111700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-111600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-116600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-112600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-108400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-105100</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5591,8 +5765,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,74 +6023,77 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>29400</v>
+        <v>90100</v>
       </c>
       <c r="E76" s="3">
-        <v>29500</v>
+        <v>30000</v>
       </c>
       <c r="F76" s="3">
-        <v>33200</v>
+        <v>30100</v>
       </c>
       <c r="G76" s="3">
-        <v>12900</v>
+        <v>33900</v>
       </c>
       <c r="H76" s="3">
-        <v>9300</v>
+        <v>13100</v>
       </c>
       <c r="I76" s="3">
-        <v>17200</v>
+        <v>9500</v>
       </c>
       <c r="J76" s="3">
+        <v>17500</v>
+      </c>
+      <c r="K76" s="3">
         <v>26400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>32700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>37800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>59900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>66500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>75100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>38500</v>
-      </c>
-      <c r="R76" s="3">
-        <v>43100</v>
       </c>
       <c r="S76" s="3">
         <v>43100</v>
       </c>
       <c r="T76" s="3">
+        <v>43100</v>
+      </c>
+      <c r="U76" s="3">
         <v>47800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>48800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-91000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-88500</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5923,8 +6109,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-8700</v>
+        <v>-10100</v>
       </c>
       <c r="E81" s="3">
-        <v>-10000</v>
+        <v>-8900</v>
       </c>
       <c r="F81" s="3">
-        <v>-9300</v>
+        <v>-10200</v>
       </c>
       <c r="G81" s="3">
-        <v>-10400</v>
+        <v>-9500</v>
       </c>
       <c r="H81" s="3">
-        <v>-12000</v>
+        <v>-10700</v>
       </c>
       <c r="I81" s="3">
-        <v>-15200</v>
+        <v>-12200</v>
       </c>
       <c r="J81" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="K81" s="3">
         <v>-10500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6800</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>-2700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,8 +6406,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6237,62 +6436,65 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>1100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>-600</v>
-      </c>
-      <c r="U83" s="3">
-        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
       </c>
       <c r="W83" s="3">
+        <v>200</v>
+      </c>
+      <c r="X83" s="3">
         <v>400</v>
-      </c>
-      <c r="X83" s="3">
-        <v>200</v>
       </c>
       <c r="Y83" s="3">
         <v>200</v>
       </c>
       <c r="Z83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA83" s="3">
         <v>400</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,8 +6920,11 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6735,62 +6952,65 @@
       <c r="K89" s="3">
         <v>0</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>-16800</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>-6100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-21100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-10900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,8 +7040,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6832,7 +7053,7 @@
         <v>-3700</v>
       </c>
       <c r="F91" s="3">
-        <v>-8300</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -6850,52 +7071,52 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-1100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-1200</v>
       </c>
       <c r="Q91" s="3">
         <v>-1200</v>
       </c>
       <c r="R91" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X91" s="3">
         <v>-100</v>
       </c>
       <c r="Y91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="Z91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
+      <c r="AA91" s="3">
+        <v>-400</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
@@ -6903,8 +7124,11 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,8 +7296,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7098,62 +7328,65 @@
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>-4600</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
         <v>-7000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>3300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1300</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7266,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,8 +7758,11 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7544,62 +7790,65 @@
       <c r="K100" s="3">
         <v>0</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>36900</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>38900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>40000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>5900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>6500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-51700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>39600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>7300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>7200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2100</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7627,62 +7876,65 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
         <v>-700</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7710,58 +7962,61 @@
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3">
         <v>14800</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3">
         <v>25600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>46300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-25300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-13800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-53100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>43100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-600</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
   <si>
     <t>EH</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>14400</v>
+        <v>18300</v>
       </c>
       <c r="E8" s="3">
-        <v>8700</v>
+        <v>14000</v>
       </c>
       <c r="F8" s="3">
+        <v>8500</v>
+      </c>
+      <c r="G8" s="3">
         <v>8000</v>
       </c>
-      <c r="G8" s="3">
-        <v>4000</v>
-      </c>
       <c r="H8" s="3">
+        <v>3900</v>
+      </c>
+      <c r="I8" s="3">
         <v>1400</v>
       </c>
-      <c r="I8" s="3">
-        <v>3100</v>
-      </c>
       <c r="J8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K8" s="3">
         <v>2200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5000</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>1600</v>
       </c>
       <c r="Z8" s="3">
         <v>1600</v>
       </c>
       <c r="AA8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AB8" s="3">
         <v>5400</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>5400</v>
+        <v>7100</v>
       </c>
       <c r="E9" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F9" s="3">
         <v>3300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>500</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K9" s="3">
+        <v>700</v>
+      </c>
+      <c r="L9" s="3">
+        <v>400</v>
+      </c>
+      <c r="M9" s="3">
+        <v>700</v>
+      </c>
+      <c r="N9" s="3">
+        <v>300</v>
+      </c>
+      <c r="O9" s="3">
+        <v>500</v>
+      </c>
+      <c r="P9" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q9" s="3">
         <v>600</v>
       </c>
-      <c r="I9" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J9" s="3">
-        <v>700</v>
-      </c>
-      <c r="K9" s="3">
-        <v>400</v>
-      </c>
-      <c r="L9" s="3">
-        <v>700</v>
-      </c>
-      <c r="M9" s="3">
-        <v>300</v>
-      </c>
-      <c r="N9" s="3">
-        <v>500</v>
-      </c>
-      <c r="O9" s="3">
-        <v>700</v>
-      </c>
-      <c r="P9" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2100</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>700</v>
       </c>
       <c r="Z9" s="3">
         <v>700</v>
       </c>
       <c r="AA9" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB9" s="3">
         <v>2500</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>9000</v>
+        <v>11200</v>
       </c>
       <c r="E10" s="3">
-        <v>5400</v>
+        <v>8800</v>
       </c>
       <c r="F10" s="3">
+        <v>5300</v>
+      </c>
+      <c r="G10" s="3">
         <v>5200</v>
       </c>
-      <c r="G10" s="3">
-        <v>2600</v>
-      </c>
       <c r="H10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I10" s="3">
         <v>800</v>
       </c>
-      <c r="I10" s="3">
-        <v>2000</v>
-      </c>
       <c r="J10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K10" s="3">
         <v>1500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5200</v>
-      </c>
-      <c r="W10" s="3">
-        <v>2900</v>
       </c>
       <c r="X10" s="3">
         <v>2900</v>
       </c>
       <c r="Y10" s="3">
-        <v>900</v>
+        <v>2900</v>
       </c>
       <c r="Z10" s="3">
         <v>900</v>
       </c>
       <c r="AA10" s="3">
+        <v>900</v>
+      </c>
+      <c r="AB10" s="3">
         <v>2900</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1070,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>8700</v>
+        <v>6300</v>
       </c>
       <c r="E12" s="3">
-        <v>5300</v>
+        <v>8500</v>
       </c>
       <c r="F12" s="3">
+        <v>5200</v>
+      </c>
+      <c r="G12" s="3">
         <v>5400</v>
       </c>
-      <c r="G12" s="3">
-        <v>5300</v>
-      </c>
       <c r="H12" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="I12" s="3">
-        <v>7600</v>
+        <v>5200</v>
       </c>
       <c r="J12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="K12" s="3">
         <v>5200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2900</v>
-      </c>
-      <c r="T12" s="3">
-        <v>2600</v>
       </c>
       <c r="U12" s="3">
         <v>2600</v>
       </c>
       <c r="V12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="W12" s="3">
         <v>2400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3900</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,31 +1259,34 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1328,31 +1348,34 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1414,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>25300</v>
+        <v>26100</v>
       </c>
       <c r="E17" s="3">
-        <v>18000</v>
+        <v>24700</v>
       </c>
       <c r="F17" s="3">
+        <v>17700</v>
+      </c>
+      <c r="G17" s="3">
         <v>18600</v>
       </c>
-      <c r="G17" s="3">
-        <v>13900</v>
-      </c>
       <c r="H17" s="3">
-        <v>12000</v>
+        <v>13500</v>
       </c>
       <c r="I17" s="3">
-        <v>13800</v>
+        <v>11800</v>
       </c>
       <c r="J17" s="3">
+        <v>14300</v>
+      </c>
+      <c r="K17" s="3">
         <v>15200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9000</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-10900</v>
+        <v>-7800</v>
       </c>
       <c r="E18" s="3">
-        <v>-9300</v>
+        <v>-10700</v>
       </c>
       <c r="F18" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-10600</v>
       </c>
-      <c r="G18" s="3">
-        <v>-9900</v>
-      </c>
       <c r="H18" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-10600</v>
       </c>
-      <c r="I18" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-14600</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-10400</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,117 +1680,121 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>400</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O20" s="3">
+        <v>300</v>
+      </c>
+      <c r="P20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3">
-        <v>300</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="S20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="N20" s="3">
-        <v>300</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>600</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>200</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>200</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-200</v>
-      </c>
-      <c r="W20" s="3">
-        <v>100</v>
       </c>
       <c r="X20" s="3">
         <v>100</v>
       </c>
       <c r="Y20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-10600</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1768,59 +1805,62 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-13300</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-8700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1840,13 +1880,13 @@
         <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
+        <v>100</v>
+      </c>
+      <c r="K22" s="3">
         <v>300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
@@ -1882,7 +1922,7 @@
         <v>100</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1896,8 +1936,8 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
+      <c r="AB22" s="3">
+        <v>0</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>3</v>
@@ -1905,94 +1945,100 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-10000</v>
+        <v>-6800</v>
       </c>
       <c r="E23" s="3">
-        <v>-8900</v>
+        <v>-9900</v>
       </c>
       <c r="F23" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="M23" s="3">
         <v>-10300</v>
       </c>
-      <c r="G23" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-10400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-12300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-15500</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-10600</v>
       </c>
-      <c r="L23" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2051,11 +2097,11 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
@@ -2066,19 +2112,22 @@
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-10000</v>
+        <v>-6900</v>
       </c>
       <c r="E26" s="3">
-        <v>-8900</v>
+        <v>-9900</v>
       </c>
       <c r="F26" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="M26" s="3">
         <v>-10300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-10400</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-12300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-15500</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-10600</v>
       </c>
-      <c r="L26" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3200</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>-1600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-10100</v>
+        <v>-6900</v>
       </c>
       <c r="E27" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="R27" s="3">
         <v>-8900</v>
       </c>
-      <c r="F27" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-12200</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-15500</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-14600</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6800</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-2700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1000</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>200</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L32" s="3">
+        <v>300</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>600</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="S32" s="3">
+        <v>100</v>
+      </c>
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>2200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>600</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="R32" s="3">
-        <v>100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>200</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-100</v>
       </c>
       <c r="X32" s="3">
         <v>-100</v>
       </c>
       <c r="Y32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>1200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-10100</v>
+        <v>-6900</v>
       </c>
       <c r="E33" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="O33" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="R33" s="3">
         <v>-8900</v>
       </c>
-      <c r="F33" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-12200</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-15500</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-14600</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6800</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-2700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-10100</v>
+        <v>-6900</v>
       </c>
       <c r="E35" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="O35" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="R35" s="3">
         <v>-8900</v>
       </c>
-      <c r="F35" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-12200</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-15500</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-14600</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6800</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-2700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,77 +3264,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>87900</v>
+        <v>87200</v>
       </c>
       <c r="E41" s="3">
-        <v>35400</v>
+        <v>85800</v>
       </c>
       <c r="F41" s="3">
+        <v>34700</v>
+      </c>
+      <c r="G41" s="3">
         <v>32200</v>
       </c>
-      <c r="G41" s="3">
-        <v>32900</v>
-      </c>
       <c r="H41" s="3">
-        <v>17900</v>
+        <v>31900</v>
       </c>
       <c r="I41" s="3">
-        <v>26000</v>
+        <v>17500</v>
       </c>
       <c r="J41" s="3">
+        <v>26800</v>
+      </c>
+      <c r="K41" s="3">
         <v>35100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>28800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>28200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>34100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>40400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>45500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>66400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>19200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>23300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>33600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>38700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>50400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9300</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3264,77 +3351,80 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>47000</v>
+        <v>60700</v>
       </c>
       <c r="E42" s="3">
-        <v>10300</v>
+        <v>45900</v>
       </c>
       <c r="F42" s="3">
         <v>10100</v>
       </c>
       <c r="G42" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
+        <v>10100</v>
+      </c>
+      <c r="H42" s="3">
+        <v>3900</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>9900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>10300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>12300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>6900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>12500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>4400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1300</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,77 +3440,80 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6900</v>
+        <v>2600</v>
       </c>
       <c r="E43" s="3">
-        <v>3100</v>
+        <v>6800</v>
       </c>
       <c r="F43" s="3">
-        <v>4900</v>
+        <v>3000</v>
       </c>
       <c r="G43" s="3">
-        <v>2600</v>
+        <v>5200</v>
       </c>
       <c r="H43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I43" s="3">
         <v>2300</v>
       </c>
-      <c r="I43" s="3">
-        <v>3500</v>
-      </c>
       <c r="J43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K43" s="3">
         <v>2900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>16300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>23200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>21200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4400</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3436,77 +3529,80 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>10000</v>
+        <v>9700</v>
       </c>
       <c r="E44" s="3">
-        <v>8800</v>
+        <v>9800</v>
       </c>
       <c r="F44" s="3">
-        <v>8400</v>
+        <v>8600</v>
       </c>
       <c r="G44" s="3">
-        <v>9200</v>
+        <v>8700</v>
       </c>
       <c r="H44" s="3">
-        <v>9900</v>
+        <v>8900</v>
       </c>
       <c r="I44" s="3">
-        <v>9300</v>
+        <v>9700</v>
       </c>
       <c r="J44" s="3">
+        <v>9600</v>
+      </c>
+      <c r="K44" s="3">
         <v>10200</v>
-      </c>
-      <c r="K44" s="3">
-        <v>11000</v>
       </c>
       <c r="L44" s="3">
         <v>11000</v>
       </c>
       <c r="M44" s="3">
+        <v>11000</v>
+      </c>
+      <c r="N44" s="3">
         <v>11800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1300</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3522,77 +3618,80 @@
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7400</v>
+        <v>10000</v>
       </c>
       <c r="E45" s="3">
-        <v>3800</v>
+        <v>7300</v>
       </c>
       <c r="F45" s="3">
-        <v>8300</v>
+        <v>3700</v>
       </c>
       <c r="G45" s="3">
-        <v>11500</v>
+        <v>6700</v>
       </c>
       <c r="H45" s="3">
-        <v>11500</v>
+        <v>11200</v>
       </c>
       <c r="I45" s="3">
-        <v>10700</v>
+        <v>11300</v>
       </c>
       <c r="J45" s="3">
+        <v>11100</v>
+      </c>
+      <c r="K45" s="3">
         <v>6400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3900</v>
-      </c>
-      <c r="R45" s="3">
-        <v>3300</v>
       </c>
       <c r="S45" s="3">
         <v>3300</v>
       </c>
       <c r="T45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="U45" s="3">
         <v>3000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3500</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,77 +3707,80 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>159300</v>
+        <v>170200</v>
       </c>
       <c r="E46" s="3">
-        <v>61300</v>
+        <v>155500</v>
       </c>
       <c r="F46" s="3">
+        <v>60200</v>
+      </c>
+      <c r="G46" s="3">
         <v>63900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
+        <v>58500</v>
+      </c>
+      <c r="I46" s="3">
+        <v>40800</v>
+      </c>
+      <c r="J46" s="3">
+        <v>51200</v>
+      </c>
+      <c r="K46" s="3">
+        <v>54600</v>
+      </c>
+      <c r="L46" s="3">
+        <v>51900</v>
+      </c>
+      <c r="M46" s="3">
+        <v>56800</v>
+      </c>
+      <c r="N46" s="3">
+        <v>58600</v>
+      </c>
+      <c r="O46" s="3">
+        <v>65900</v>
+      </c>
+      <c r="P46" s="3">
+        <v>78600</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>86200</v>
+      </c>
+      <c r="R46" s="3">
+        <v>93300</v>
+      </c>
+      <c r="S46" s="3">
+        <v>59100</v>
+      </c>
+      <c r="T46" s="3">
+        <v>68600</v>
+      </c>
+      <c r="U46" s="3">
         <v>60200</v>
       </c>
-      <c r="H46" s="3">
-        <v>41700</v>
-      </c>
-      <c r="I46" s="3">
-        <v>49500</v>
-      </c>
-      <c r="J46" s="3">
-        <v>54600</v>
-      </c>
-      <c r="K46" s="3">
-        <v>51900</v>
-      </c>
-      <c r="L46" s="3">
-        <v>56800</v>
-      </c>
-      <c r="M46" s="3">
-        <v>58600</v>
-      </c>
-      <c r="N46" s="3">
-        <v>65900</v>
-      </c>
-      <c r="O46" s="3">
-        <v>78600</v>
-      </c>
-      <c r="P46" s="3">
-        <v>86200</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>93300</v>
-      </c>
-      <c r="R46" s="3">
-        <v>59100</v>
-      </c>
-      <c r="S46" s="3">
-        <v>68600</v>
-      </c>
-      <c r="T46" s="3">
-        <v>60200</v>
-      </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>57400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>67100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>25000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>19800</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3694,67 +3796,70 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F47" s="3">
         <v>2500</v>
       </c>
-      <c r="E47" s="3">
-        <v>2500</v>
-      </c>
-      <c r="F47" s="3">
-        <v>3200</v>
-      </c>
       <c r="G47" s="3">
-        <v>3300</v>
+        <v>2600</v>
       </c>
       <c r="H47" s="3">
-        <v>3100</v>
+        <v>2200</v>
       </c>
       <c r="I47" s="3">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="J47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K47" s="3">
         <v>2800</v>
-      </c>
-      <c r="K47" s="3">
-        <v>1400</v>
       </c>
       <c r="L47" s="3">
         <v>1400</v>
       </c>
       <c r="M47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N47" s="3">
         <v>1100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2400</v>
-      </c>
-      <c r="P47" s="3">
-        <v>2300</v>
       </c>
       <c r="Q47" s="3">
         <v>2300</v>
       </c>
       <c r="R47" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S47" s="3">
         <v>2500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7500</v>
-      </c>
-      <c r="V47" s="3">
-        <v>500</v>
       </c>
       <c r="W47" s="3">
         <v>500</v>
@@ -3762,8 +3867,8 @@
       <c r="X47" s="3">
         <v>500</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
+      <c r="Y47" s="3">
+        <v>500</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
@@ -3780,77 +3885,80 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>22900</v>
+        <v>23900</v>
       </c>
       <c r="E48" s="3">
-        <v>19200</v>
+        <v>22400</v>
       </c>
       <c r="F48" s="3">
+        <v>18800</v>
+      </c>
+      <c r="G48" s="3">
         <v>16800</v>
       </c>
-      <c r="G48" s="3">
-        <v>17200</v>
-      </c>
       <c r="H48" s="3">
-        <v>16500</v>
+        <v>16800</v>
       </c>
       <c r="I48" s="3">
-        <v>16400</v>
+        <v>16200</v>
       </c>
       <c r="J48" s="3">
         <v>17000</v>
       </c>
       <c r="K48" s="3">
+        <v>17000</v>
+      </c>
+      <c r="L48" s="3">
         <v>16000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2300</v>
-      </c>
-      <c r="V48" s="3">
-        <v>2500</v>
       </c>
       <c r="W48" s="3">
         <v>2500</v>
       </c>
       <c r="X48" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Y48" s="3">
         <v>2700</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3974,11 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3875,10 +3986,10 @@
         <v>300</v>
       </c>
       <c r="E49" s="3">
+        <v>300</v>
+      </c>
+      <c r="F49" s="3">
         <v>400</v>
-      </c>
-      <c r="F49" s="3">
-        <v>300</v>
       </c>
       <c r="G49" s="3">
         <v>300</v>
@@ -3893,10 +4004,10 @@
         <v>300</v>
       </c>
       <c r="K49" s="3">
+        <v>300</v>
+      </c>
+      <c r="L49" s="3">
         <v>200</v>
-      </c>
-      <c r="L49" s="3">
-        <v>100</v>
       </c>
       <c r="M49" s="3">
         <v>100</v>
@@ -3917,7 +4028,7 @@
         <v>100</v>
       </c>
       <c r="S49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T49" s="3">
         <v>200</v>
@@ -3929,13 +4040,13 @@
         <v>200</v>
       </c>
       <c r="W49" s="3">
+        <v>200</v>
+      </c>
+      <c r="X49" s="3">
         <v>100</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
+      <c r="Y49" s="3">
+        <v>0</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
@@ -3952,8 +4063,11 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,8 +4241,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4133,7 +4253,7 @@
         <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F52" s="3">
         <v>200</v>
@@ -4157,7 +4277,7 @@
         <v>200</v>
       </c>
       <c r="M52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N52" s="3">
         <v>300</v>
@@ -4166,16 +4286,16 @@
         <v>300</v>
       </c>
       <c r="P52" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q52" s="3">
         <v>500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2800</v>
-      </c>
-      <c r="S52" s="3">
-        <v>100</v>
       </c>
       <c r="T52" s="3">
         <v>100</v>
@@ -4192,8 +4312,8 @@
       <c r="X52" s="3">
         <v>100</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
+      <c r="Y52" s="3">
+        <v>100</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
@@ -4210,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,77 +4419,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>185300</v>
+        <v>198000</v>
       </c>
       <c r="E54" s="3">
-        <v>83600</v>
+        <v>180900</v>
       </c>
       <c r="F54" s="3">
+        <v>82100</v>
+      </c>
+      <c r="G54" s="3">
         <v>84400</v>
       </c>
-      <c r="G54" s="3">
-        <v>81300</v>
-      </c>
       <c r="H54" s="3">
-        <v>61900</v>
+        <v>79100</v>
       </c>
       <c r="I54" s="3">
-        <v>69000</v>
+        <v>60500</v>
       </c>
       <c r="J54" s="3">
+        <v>71200</v>
+      </c>
+      <c r="K54" s="3">
         <v>74800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>69700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>65600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>67400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>73900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>86500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>94000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>103100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>67400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>73200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>69500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>67400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>70400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>28000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>23000</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4382,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,77 +4576,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10400</v>
+        <v>14900</v>
       </c>
       <c r="E57" s="3">
-        <v>5900</v>
+        <v>10200</v>
       </c>
       <c r="F57" s="3">
-        <v>4900</v>
+        <v>5800</v>
       </c>
       <c r="G57" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J57" s="3">
         <v>4700</v>
       </c>
-      <c r="H57" s="3">
-        <v>4700</v>
-      </c>
-      <c r="I57" s="3">
-        <v>4500</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5500</v>
-      </c>
-      <c r="N57" s="3">
-        <v>6300</v>
       </c>
       <c r="O57" s="3">
         <v>6300</v>
       </c>
       <c r="P57" s="3">
-        <v>5100</v>
+        <v>6300</v>
       </c>
       <c r="Q57" s="3">
         <v>5100</v>
       </c>
       <c r="R57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="S57" s="3">
         <v>7400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2600</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,64 +4663,67 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>23000</v>
+        <v>25700</v>
       </c>
       <c r="E58" s="3">
-        <v>6100</v>
+        <v>23900</v>
       </c>
       <c r="F58" s="3">
-        <v>10300</v>
+        <v>7000</v>
       </c>
       <c r="G58" s="3">
-        <v>6100</v>
+        <v>11100</v>
       </c>
       <c r="H58" s="3">
-        <v>8600</v>
+        <v>6900</v>
       </c>
       <c r="I58" s="3">
-        <v>19800</v>
+        <v>9300</v>
       </c>
       <c r="J58" s="3">
+        <v>21100</v>
+      </c>
+      <c r="K58" s="3">
         <v>17000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1800</v>
-      </c>
-      <c r="O58" s="3">
-        <v>1400</v>
       </c>
       <c r="P58" s="3">
         <v>1400</v>
       </c>
       <c r="Q58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R58" s="3">
         <v>2200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1500</v>
-      </c>
-      <c r="U58" s="3">
-        <v>800</v>
       </c>
       <c r="V58" s="3">
         <v>800</v>
@@ -4598,11 +4732,11 @@
         <v>800</v>
       </c>
       <c r="X58" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y58" s="3">
         <v>1600</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4618,77 +4752,80 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>41500</v>
+        <v>13800</v>
       </c>
       <c r="E59" s="3">
-        <v>19100</v>
+        <v>24900</v>
       </c>
       <c r="F59" s="3">
-        <v>20000</v>
+        <v>6600</v>
       </c>
       <c r="G59" s="3">
-        <v>17200</v>
+        <v>9100</v>
       </c>
       <c r="H59" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I59" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K59" s="3">
         <v>17800</v>
       </c>
-      <c r="I59" s="3">
-        <v>17700</v>
-      </c>
-      <c r="J59" s="3">
-        <v>17800</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10800</v>
-      </c>
-      <c r="R59" s="3">
-        <v>12500</v>
       </c>
       <c r="S59" s="3">
         <v>12500</v>
       </c>
       <c r="T59" s="3">
+        <v>12500</v>
+      </c>
+      <c r="U59" s="3">
         <v>7100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5100</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4704,77 +4841,80 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>75000</v>
+        <v>71300</v>
       </c>
       <c r="E60" s="3">
-        <v>31100</v>
+        <v>73200</v>
       </c>
       <c r="F60" s="3">
+        <v>30600</v>
+      </c>
+      <c r="G60" s="3">
         <v>35300</v>
       </c>
-      <c r="G60" s="3">
-        <v>28000</v>
-      </c>
       <c r="H60" s="3">
-        <v>31200</v>
+        <v>27200</v>
       </c>
       <c r="I60" s="3">
-        <v>42000</v>
+        <v>30500</v>
       </c>
       <c r="J60" s="3">
+        <v>43400</v>
+      </c>
+      <c r="K60" s="3">
         <v>39800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>16900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>22500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>15000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9300</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,77 +4930,80 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2000</v>
+        <v>18600</v>
       </c>
       <c r="E61" s="3">
-        <v>2200</v>
+        <v>18300</v>
       </c>
       <c r="F61" s="3">
-        <v>1300</v>
+        <v>15100</v>
       </c>
       <c r="G61" s="3">
-        <v>1500</v>
+        <v>11900</v>
       </c>
       <c r="H61" s="3">
-        <v>400</v>
+        <v>11900</v>
       </c>
       <c r="I61" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J61" s="3">
+        <v>10600</v>
+      </c>
+      <c r="K61" s="3">
         <v>500</v>
-      </c>
-      <c r="J61" s="3">
-        <v>500</v>
-      </c>
-      <c r="K61" s="3">
-        <v>600</v>
       </c>
       <c r="L61" s="3">
         <v>600</v>
       </c>
       <c r="M61" s="3">
+        <v>600</v>
+      </c>
+      <c r="N61" s="3">
         <v>700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2300</v>
-      </c>
-      <c r="O61" s="3">
-        <v>2800</v>
       </c>
       <c r="P61" s="3">
         <v>2800</v>
       </c>
       <c r="Q61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="R61" s="3">
         <v>2900</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>4600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>300</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4876,46 +5019,49 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>18300</v>
+        <v>1500</v>
       </c>
       <c r="E62" s="3">
-        <v>14600</v>
+        <v>1300</v>
       </c>
       <c r="F62" s="3">
-        <v>12000</v>
+        <v>1100</v>
       </c>
       <c r="G62" s="3">
-        <v>12100</v>
+        <v>1100</v>
       </c>
       <c r="H62" s="3">
-        <v>11400</v>
+        <v>1100</v>
       </c>
       <c r="I62" s="3">
-        <v>11200</v>
+        <v>1000</v>
       </c>
       <c r="J62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K62" s="3">
         <v>11300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1100</v>
-      </c>
-      <c r="O62" s="3">
-        <v>1200</v>
       </c>
       <c r="P62" s="3">
         <v>1200</v>
@@ -4927,25 +5073,25 @@
         <v>1200</v>
       </c>
       <c r="S62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="T62" s="3">
         <v>1300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>800</v>
-      </c>
-      <c r="U62" s="3">
-        <v>900</v>
       </c>
       <c r="V62" s="3">
         <v>900</v>
       </c>
       <c r="W62" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="X62" s="3">
         <v>800</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
+      <c r="Y62" s="3">
+        <v>800</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,77 +5375,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>95200</v>
+        <v>91500</v>
       </c>
       <c r="E66" s="3">
-        <v>53600</v>
+        <v>92900</v>
       </c>
       <c r="F66" s="3">
-        <v>54300</v>
+        <v>47000</v>
       </c>
       <c r="G66" s="3">
-        <v>47400</v>
+        <v>48600</v>
       </c>
       <c r="H66" s="3">
-        <v>48700</v>
+        <v>40500</v>
       </c>
       <c r="I66" s="3">
-        <v>59400</v>
+        <v>42100</v>
       </c>
       <c r="J66" s="3">
+        <v>55400</v>
+      </c>
+      <c r="K66" s="3">
         <v>57300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>43300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>29600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>26600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>27500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>30100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>26400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>21600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10700</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5306,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5573,14 +5741,14 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>102400</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>100800</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,77 +5853,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-266200</v>
+        <v>-276000</v>
       </c>
       <c r="E72" s="3">
-        <v>-256100</v>
+        <v>-259800</v>
       </c>
       <c r="F72" s="3">
-        <v>-247200</v>
+        <v>-251600</v>
       </c>
       <c r="G72" s="3">
-        <v>-237000</v>
+        <v>-247300</v>
       </c>
       <c r="H72" s="3">
-        <v>-227500</v>
+        <v>-230400</v>
       </c>
       <c r="I72" s="3">
-        <v>-216900</v>
+        <v>-222500</v>
       </c>
       <c r="J72" s="3">
+        <v>-224000</v>
+      </c>
+      <c r="K72" s="3">
         <v>-204300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-185000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-175600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-164300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-154800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-144400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-134100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-124800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-112300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-111700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-111600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-116600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-112600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-108400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-105100</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5768,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,77 +6209,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>90100</v>
+        <v>106400</v>
       </c>
       <c r="E76" s="3">
-        <v>30000</v>
+        <v>87900</v>
       </c>
       <c r="F76" s="3">
-        <v>30100</v>
+        <v>29500</v>
       </c>
       <c r="G76" s="3">
-        <v>33900</v>
+        <v>30200</v>
       </c>
       <c r="H76" s="3">
-        <v>13100</v>
+        <v>33000</v>
       </c>
       <c r="I76" s="3">
-        <v>9500</v>
+        <v>12900</v>
       </c>
       <c r="J76" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K76" s="3">
         <v>17500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>32700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>59900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>66500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>75100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>38500</v>
-      </c>
-      <c r="S76" s="3">
-        <v>43100</v>
       </c>
       <c r="T76" s="3">
         <v>43100</v>
       </c>
       <c r="U76" s="3">
+        <v>43100</v>
+      </c>
+      <c r="V76" s="3">
         <v>47800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>48800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-91000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-88500</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6112,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-10100</v>
+        <v>-6900</v>
       </c>
       <c r="E81" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="O81" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="R81" s="3">
         <v>-8900</v>
       </c>
-      <c r="F81" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-12200</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-15500</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-14600</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6800</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-2700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,31 +6605,32 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -6439,62 +6638,65 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>1100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>-600</v>
-      </c>
-      <c r="V83" s="3">
-        <v>200</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
       </c>
       <c r="X83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y83" s="3">
         <v>400</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>200</v>
       </c>
       <c r="Z83" s="3">
         <v>200</v>
       </c>
       <c r="AA83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB83" s="3">
         <v>400</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,31 +7137,34 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -6955,62 +7172,65 @@
       <c r="L89" s="3">
         <v>0</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>-16800</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-21100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-10900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,31 +7261,32 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -7074,52 +7295,52 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-1200</v>
       </c>
       <c r="R91" s="3">
         <v>-1200</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y91" s="3">
         <v>-100</v>
       </c>
       <c r="Z91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
+      <c r="AB91" s="3">
+        <v>-400</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
@@ -7127,8 +7348,11 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,31 +7526,34 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -7331,62 +7561,65 @@
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>-4600</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>3300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1300</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,31 +7650,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,31 +8004,34 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -7793,85 +8039,88 @@
       <c r="L100" s="3">
         <v>0</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>36900</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>38900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>40000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>5900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>6500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-51700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>39600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>7300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>7200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2100</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7879,62 +8128,65 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>-700</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7965,58 +8217,61 @@
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>14800</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3">
         <v>25600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>46300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-25300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-10400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-13800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-53100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>43100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-600</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
   <si>
     <t>EH</t>
   </si>
@@ -656,403 +656,415 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E8" s="3">
         <v>18300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5000</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>1600</v>
       </c>
       <c r="AA8" s="3">
         <v>1600</v>
       </c>
       <c r="AB8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AC8" s="3">
         <v>5400</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E9" s="3">
         <v>7100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2100</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>700</v>
       </c>
       <c r="AA9" s="3">
         <v>700</v>
       </c>
       <c r="AB9" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC9" s="3">
         <v>2500</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E10" s="3">
         <v>11200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5200</v>
-      </c>
-      <c r="X10" s="3">
-        <v>2900</v>
       </c>
       <c r="Y10" s="3">
         <v>2900</v>
       </c>
       <c r="Z10" s="3">
-        <v>900</v>
+        <v>2900</v>
       </c>
       <c r="AA10" s="3">
         <v>900</v>
       </c>
       <c r="AB10" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC10" s="3">
         <v>2900</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,97 +1096,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E12" s="3">
         <v>6300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5400</v>
-      </c>
-      <c r="H12" s="3">
-        <v>5200</v>
       </c>
       <c r="I12" s="3">
         <v>5200</v>
       </c>
       <c r="J12" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K12" s="3">
         <v>7900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2900</v>
-      </c>
-      <c r="U12" s="3">
-        <v>2600</v>
       </c>
       <c r="V12" s="3">
         <v>2600</v>
       </c>
       <c r="W12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="X12" s="3">
         <v>2400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3900</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1278,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1276,11 +1295,11 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1288,8 +1307,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1351,8 +1370,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1369,7 +1391,7 @@
         <v>500</v>
       </c>
       <c r="H15" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
         <v>300</v>
@@ -1378,7 +1400,7 @@
         <v>300</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1440,8 +1462,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1495,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E17" s="3">
         <v>26100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9000</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-14600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-10400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,97 +1713,101 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-200</v>
-      </c>
-      <c r="X20" s="3">
-        <v>100</v>
       </c>
       <c r="Y20" s="3">
         <v>100</v>
       </c>
       <c r="Z20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1779,26 +1815,26 @@
         <v>-7500</v>
       </c>
       <c r="E21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-10200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-10200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10600</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,59 +1844,62 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-13300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-10000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-8700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1886,10 +1925,10 @@
         <v>100</v>
       </c>
       <c r="K22" s="3">
+        <v>100</v>
+      </c>
+      <c r="L22" s="3">
         <v>300</v>
-      </c>
-      <c r="L22" s="3">
-        <v>100</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
@@ -1925,7 +1964,7 @@
         <v>100</v>
       </c>
       <c r="X22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -1939,8 +1978,8 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
+      <c r="AC22" s="3">
+        <v>0</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
@@ -1948,97 +1987,103 @@
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2100,11 +2145,11 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
@@ -2115,19 +2160,22 @@
         <v>0</v>
       </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2263,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-15500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3200</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
       <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-15500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6800</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-2700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2539,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2631,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2723,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2815,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>200</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-100</v>
       </c>
       <c r="Y32" s="3">
         <v>-100</v>
       </c>
       <c r="Z32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>1200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-15500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6800</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-2700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3091,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-15500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6800</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-2700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3316,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,80 +3350,81 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>83700</v>
+      </c>
+      <c r="E41" s="3">
         <v>87200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>85800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>34700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>32200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>31900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>35100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>28800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>28200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>34100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>40400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>45500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>66400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>19200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>23300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>33600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>38700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>50400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9300</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3354,29 +3440,32 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E42" s="3">
         <v>60700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>45900</v>
-      </c>
-      <c r="F42" s="3">
-        <v>10100</v>
       </c>
       <c r="G42" s="3">
         <v>10100</v>
       </c>
       <c r="H42" s="3">
+        <v>10100</v>
+      </c>
+      <c r="I42" s="3">
         <v>3900</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -3384,50 +3473,50 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>9900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>10300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>12300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>6900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>12500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>4400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1300</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3443,80 +3532,83 @@
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>16300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>14200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>23200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>21200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>9400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4400</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,80 +3624,83 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E44" s="3">
         <v>9700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>8600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>8700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10200</v>
-      </c>
-      <c r="L44" s="3">
-        <v>11000</v>
       </c>
       <c r="M44" s="3">
         <v>11000</v>
       </c>
       <c r="N44" s="3">
+        <v>11000</v>
+      </c>
+      <c r="O44" s="3">
         <v>11800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>7100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1300</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,80 +3716,83 @@
       <c r="AE44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E45" s="3">
         <v>10000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3900</v>
-      </c>
-      <c r="S45" s="3">
-        <v>3300</v>
       </c>
       <c r="T45" s="3">
         <v>3300</v>
       </c>
       <c r="U45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="V45" s="3">
         <v>3000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3500</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3710,80 +3808,83 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>185900</v>
+      </c>
+      <c r="E46" s="3">
         <v>170200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>155500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>60200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>63900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>58500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>40800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>51200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>54600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>51900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>56800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>58600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>65900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>78600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>86200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>93300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>59100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>68600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>60200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>57400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>67100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>25000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>19800</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3799,70 +3900,73 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E47" s="3">
         <v>3200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2800</v>
-      </c>
-      <c r="L47" s="3">
-        <v>1400</v>
       </c>
       <c r="M47" s="3">
         <v>1400</v>
       </c>
       <c r="N47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O47" s="3">
         <v>1100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2400</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>2300</v>
       </c>
       <c r="R47" s="3">
         <v>2300</v>
       </c>
       <c r="S47" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T47" s="3">
         <v>2500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7500</v>
-      </c>
-      <c r="W47" s="3">
-        <v>500</v>
       </c>
       <c r="X47" s="3">
         <v>500</v>
@@ -3870,8 +3974,8 @@
       <c r="Y47" s="3">
         <v>500</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
+      <c r="Z47" s="3">
+        <v>500</v>
       </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
@@ -3888,80 +3992,83 @@
       <c r="AE47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E48" s="3">
         <v>23900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18800</v>
-      </c>
-      <c r="G48" s="3">
-        <v>16800</v>
       </c>
       <c r="H48" s="3">
         <v>16800</v>
       </c>
       <c r="I48" s="3">
+        <v>16800</v>
+      </c>
+      <c r="J48" s="3">
         <v>16200</v>
-      </c>
-      <c r="J48" s="3">
-        <v>17000</v>
       </c>
       <c r="K48" s="3">
         <v>17000</v>
       </c>
       <c r="L48" s="3">
+        <v>17000</v>
+      </c>
+      <c r="M48" s="3">
         <v>16000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2300</v>
-      </c>
-      <c r="W48" s="3">
-        <v>2500</v>
       </c>
       <c r="X48" s="3">
         <v>2500</v>
       </c>
       <c r="Y48" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Z48" s="3">
         <v>2700</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3977,22 +4084,25 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E49" s="3">
         <v>300</v>
       </c>
       <c r="F49" s="3">
+        <v>300</v>
+      </c>
+      <c r="G49" s="3">
         <v>400</v>
-      </c>
-      <c r="G49" s="3">
-        <v>300</v>
       </c>
       <c r="H49" s="3">
         <v>300</v>
@@ -4007,10 +4117,10 @@
         <v>300</v>
       </c>
       <c r="L49" s="3">
+        <v>300</v>
+      </c>
+      <c r="M49" s="3">
         <v>200</v>
-      </c>
-      <c r="M49" s="3">
-        <v>100</v>
       </c>
       <c r="N49" s="3">
         <v>100</v>
@@ -4031,7 +4141,7 @@
         <v>100</v>
       </c>
       <c r="T49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U49" s="3">
         <v>200</v>
@@ -4043,13 +4153,13 @@
         <v>200</v>
       </c>
       <c r="X49" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y49" s="3">
         <v>100</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
+      <c r="Z49" s="3">
+        <v>0</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
@@ -4066,8 +4176,11 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4268,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4360,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4256,7 +4375,7 @@
         <v>300</v>
       </c>
       <c r="F52" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G52" s="3">
         <v>200</v>
@@ -4280,7 +4399,7 @@
         <v>200</v>
       </c>
       <c r="N52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O52" s="3">
         <v>300</v>
@@ -4289,16 +4408,16 @@
         <v>300</v>
       </c>
       <c r="Q52" s="3">
+        <v>300</v>
+      </c>
+      <c r="R52" s="3">
         <v>500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2800</v>
-      </c>
-      <c r="T52" s="3">
-        <v>100</v>
       </c>
       <c r="U52" s="3">
         <v>100</v>
@@ -4315,8 +4434,8 @@
       <c r="Y52" s="3">
         <v>100</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
+      <c r="Z52" s="3">
+        <v>100</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
@@ -4333,8 +4452,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,80 +4544,83 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>217100</v>
+      </c>
+      <c r="E54" s="3">
         <v>198000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>180900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>82100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>84400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>79100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>60500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>71200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>74800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>69700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>65600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>67400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>73900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>86500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>94000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>103100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>67400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>73200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>69500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>67400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>70400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>28000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>23000</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4511,8 +4636,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4672,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,80 +4706,81 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E57" s="3">
         <v>14900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>4600</v>
       </c>
       <c r="I57" s="3">
         <v>4600</v>
       </c>
       <c r="J57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K57" s="3">
         <v>4700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5500</v>
-      </c>
-      <c r="O57" s="3">
-        <v>6300</v>
       </c>
       <c r="P57" s="3">
         <v>6300</v>
       </c>
       <c r="Q57" s="3">
-        <v>5100</v>
+        <v>6300</v>
       </c>
       <c r="R57" s="3">
         <v>5100</v>
       </c>
       <c r="S57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="T57" s="3">
         <v>7400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2600</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4666,67 +4796,70 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E58" s="3">
         <v>25700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>23900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>21100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1800</v>
-      </c>
-      <c r="P58" s="3">
-        <v>1400</v>
       </c>
       <c r="Q58" s="3">
         <v>1400</v>
       </c>
       <c r="R58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S58" s="3">
         <v>2200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1500</v>
-      </c>
-      <c r="V58" s="3">
-        <v>800</v>
       </c>
       <c r="W58" s="3">
         <v>800</v>
@@ -4735,11 +4868,11 @@
         <v>800</v>
       </c>
       <c r="Y58" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z58" s="3">
         <v>1600</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4755,80 +4888,83 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E59" s="3">
         <v>13800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>24900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10800</v>
-      </c>
-      <c r="S59" s="3">
-        <v>12500</v>
       </c>
       <c r="T59" s="3">
         <v>12500</v>
       </c>
       <c r="U59" s="3">
+        <v>12500</v>
+      </c>
+      <c r="V59" s="3">
         <v>7100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5100</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4844,80 +4980,83 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E60" s="3">
         <v>71300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>73200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>35300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>27200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>43400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>39800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>24100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>16900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>22000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>22500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>14600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>13300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>15000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9300</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4933,80 +5072,83 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15100</v>
-      </c>
-      <c r="G61" s="3">
-        <v>11900</v>
       </c>
       <c r="H61" s="3">
         <v>11900</v>
       </c>
       <c r="I61" s="3">
+        <v>11900</v>
+      </c>
+      <c r="J61" s="3">
         <v>10200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>500</v>
-      </c>
-      <c r="L61" s="3">
-        <v>600</v>
       </c>
       <c r="M61" s="3">
         <v>600</v>
       </c>
       <c r="N61" s="3">
+        <v>600</v>
+      </c>
+      <c r="O61" s="3">
         <v>700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2300</v>
-      </c>
-      <c r="P61" s="3">
-        <v>2800</v>
       </c>
       <c r="Q61" s="3">
         <v>2800</v>
       </c>
       <c r="R61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="S61" s="3">
         <v>2900</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>4600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>300</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5022,19 +5164,22 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1100</v>
       </c>
       <c r="G62" s="3">
         <v>1100</v>
@@ -5043,28 +5188,28 @@
         <v>1100</v>
       </c>
       <c r="I62" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="J62" s="3">
         <v>1000</v>
       </c>
       <c r="K62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L62" s="3">
         <v>11300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1100</v>
-      </c>
-      <c r="P62" s="3">
-        <v>1200</v>
       </c>
       <c r="Q62" s="3">
         <v>1200</v>
@@ -5076,25 +5221,25 @@
         <v>1200</v>
       </c>
       <c r="T62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U62" s="3">
         <v>1300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>800</v>
-      </c>
-      <c r="V62" s="3">
-        <v>900</v>
       </c>
       <c r="W62" s="3">
         <v>900</v>
       </c>
       <c r="X62" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="Y62" s="3">
         <v>800</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
+      <c r="Z62" s="3">
+        <v>800</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
@@ -5111,8 +5256,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5348,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5440,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,80 +5532,83 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>86100</v>
+      </c>
+      <c r="E66" s="3">
         <v>91500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>92900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>40500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>42100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>55400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>57300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>43300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>26600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>27500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>29000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>30100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>26400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>21600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10700</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,8 +5624,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5660,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5750,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5842,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5744,14 +5911,14 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>102400</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>100800</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
@@ -5767,8 +5934,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,80 +6026,83 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-271700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-276000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-259800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-251600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-247300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-230400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-222500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-224000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-204300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-185000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-175600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-164300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-154800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-144400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-134100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-124800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-112300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-111700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-111600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-116600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-112600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-108400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-105100</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5945,8 +6118,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6210,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6302,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,80 +6394,83 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>130900</v>
+      </c>
+      <c r="E76" s="3">
         <v>106400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>87900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>29500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>30200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>33000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>26400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>32700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>37800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>59900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>66500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>75100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>38500</v>
-      </c>
-      <c r="T76" s="3">
-        <v>43100</v>
       </c>
       <c r="U76" s="3">
         <v>43100</v>
       </c>
       <c r="V76" s="3">
+        <v>43100</v>
+      </c>
+      <c r="W76" s="3">
         <v>47800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>48800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-91000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-88500</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6301,8 +6486,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6578,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-15500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6800</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-2700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6803,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6632,8 +6830,8 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -6641,62 +6839,65 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>1100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>-600</v>
-      </c>
-      <c r="W83" s="3">
-        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
       </c>
       <c r="Y83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z83" s="3">
         <v>400</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>200</v>
       </c>
       <c r="AA83" s="3">
         <v>200</v>
       </c>
       <c r="AB83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC83" s="3">
         <v>400</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6985,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7077,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7169,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7261,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,8 +7353,11 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7166,8 +7382,8 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -7175,62 +7391,65 @@
       <c r="M89" s="3">
         <v>0</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>-16800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>-6100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-21100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-10900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7481,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7288,8 +7508,8 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -7298,52 +7518,52 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-1100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-1200</v>
       </c>
       <c r="S91" s="3">
         <v>-1200</v>
       </c>
       <c r="T91" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z91" s="3">
         <v>-100</v>
       </c>
       <c r="AA91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="AB91" s="3">
         <v>-400</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
+      <c r="AC91" s="3">
+        <v>-400</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
@@ -7351,8 +7571,11 @@
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7663,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7755,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7555,8 +7784,8 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -7564,62 +7793,65 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
         <v>-4600</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>-7000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>3300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1300</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7883,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7677,8 +7910,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7740,8 +7973,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8065,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8157,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8249,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8033,8 +8278,8 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -8042,62 +8287,65 @@
       <c r="M100" s="3">
         <v>0</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>36900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>38900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>40000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>5900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>6500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-51700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>39600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>7300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>7200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2100</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8122,8 +8370,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8131,62 +8379,65 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
         <v>-700</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8220,58 +8471,61 @@
       <c r="M102" s="3">
         <v>0</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3">
         <v>14800</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>25600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>46300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-25300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-10400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-13800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-53100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>43100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-600</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="92">
   <si>
     <t>EH</t>
   </si>
@@ -1298,8 +1298,8 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1502,7 +1502,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>30100</v>
+        <v>30200</v>
       </c>
       <c r="E17" s="3">
         <v>26100</v>
@@ -1594,7 +1594,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-7600</v>
+        <v>-7700</v>
       </c>
       <c r="E18" s="3">
         <v>-7800</v>
@@ -1720,7 +1720,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
         <v>200</v>
@@ -1824,7 +1824,7 @@
         <v>-8600</v>
       </c>
       <c r="H21" s="3">
-        <v>-10200</v>
+        <v>-10300</v>
       </c>
       <c r="I21" s="3">
         <v>-9100</v>
@@ -2824,7 +2824,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
         <v>-200</v>
@@ -3449,7 +3449,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>70400</v>
+        <v>72600</v>
       </c>
       <c r="E42" s="3">
         <v>60700</v>
@@ -3461,7 +3461,7 @@
         <v>10100</v>
       </c>
       <c r="H42" s="3">
-        <v>10100</v>
+        <v>10300</v>
       </c>
       <c r="I42" s="3">
         <v>3900</v>
@@ -3633,7 +3633,7 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>10400</v>
+        <v>13100</v>
       </c>
       <c r="E44" s="3">
         <v>9700</v>
@@ -3725,7 +3725,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>13500</v>
+        <v>7600</v>
       </c>
       <c r="E45" s="3">
         <v>10000</v>
@@ -3737,7 +3737,7 @@
         <v>3700</v>
       </c>
       <c r="H45" s="3">
-        <v>6700</v>
+        <v>6500</v>
       </c>
       <c r="I45" s="3">
         <v>11200</v>
@@ -4897,7 +4897,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>14400</v>
+        <v>17900</v>
       </c>
       <c r="E59" s="3">
         <v>13800</v>

--- a/AAII_Financials/Quarterly/EH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="92">
   <si>
     <t>EH</t>
   </si>
@@ -656,415 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E8" s="3">
         <v>22500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>18300</v>
       </c>
-      <c r="F8" s="3">
-        <v>14000</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>8500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5000</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>1600</v>
       </c>
       <c r="AB8" s="3">
         <v>1600</v>
       </c>
       <c r="AC8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AD8" s="3">
         <v>5400</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E9" s="3">
         <v>8800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7100</v>
       </c>
-      <c r="F9" s="3">
-        <v>5300</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3">
         <v>3300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2100</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>700</v>
       </c>
       <c r="AB9" s="3">
         <v>700</v>
       </c>
       <c r="AC9" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD9" s="3">
         <v>2500</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E10" s="3">
         <v>13700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11200</v>
       </c>
-      <c r="F10" s="3">
-        <v>8800</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
         <v>5300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5200</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>2900</v>
       </c>
       <c r="Z10" s="3">
         <v>2900</v>
       </c>
       <c r="AA10" s="3">
-        <v>900</v>
+        <v>2900</v>
       </c>
       <c r="AB10" s="3">
         <v>900</v>
       </c>
       <c r="AC10" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD10" s="3">
         <v>2900</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1097,100 +1110,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E12" s="3">
         <v>7700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6300</v>
       </c>
-      <c r="F12" s="3">
-        <v>8500</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
         <v>5200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5400</v>
-      </c>
-      <c r="I12" s="3">
-        <v>5200</v>
       </c>
       <c r="J12" s="3">
         <v>5200</v>
       </c>
       <c r="K12" s="3">
+        <v>5200</v>
+      </c>
+      <c r="L12" s="3">
         <v>7900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2900</v>
-      </c>
-      <c r="V12" s="3">
-        <v>2600</v>
       </c>
       <c r="W12" s="3">
         <v>2600</v>
       </c>
       <c r="X12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Y12" s="3">
         <v>2400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3900</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1310,8 +1330,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1373,8 +1393,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1388,13 +1411,13 @@
         <v>500</v>
       </c>
       <c r="G15" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>500</v>
       </c>
       <c r="I15" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="J15" s="3">
         <v>300</v>
@@ -1403,7 +1426,7 @@
         <v>300</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1465,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1496,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E17" s="3">
         <v>30200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>26100</v>
       </c>
-      <c r="F17" s="3">
-        <v>24700</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3">
         <v>17700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9000</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7800</v>
       </c>
-      <c r="F18" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3">
         <v>-9100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-14600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-10600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-6800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,130 +1747,134 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>200</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
+        <v>200</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>100</v>
       </c>
       <c r="Z20" s="3">
         <v>100</v>
       </c>
       <c r="AA20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-7500</v>
+        <v>-11800</v>
       </c>
       <c r="E21" s="3">
         <v>-7500</v>
       </c>
       <c r="F21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-10200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10600</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1847,64 +1884,67 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-10000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-8700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-6100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
@@ -1912,8 +1952,8 @@
       <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
-        <v>100</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
@@ -1928,10 +1968,10 @@
         <v>100</v>
       </c>
       <c r="L22" s="3">
+        <v>100</v>
+      </c>
+      <c r="M22" s="3">
         <v>300</v>
-      </c>
-      <c r="M22" s="3">
-        <v>100</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
@@ -1967,7 +2007,7 @@
         <v>100</v>
       </c>
       <c r="Y22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -1981,8 +2021,8 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
+      <c r="AD22" s="3">
+        <v>0</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>3</v>
@@ -1990,100 +2030,106 @@
       <c r="AF22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6800</v>
       </c>
-      <c r="F23" s="3">
-        <v>-9900</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3">
         <v>-8800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2096,8 +2142,8 @@
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -2148,11 +2194,11 @@
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
@@ -2163,19 +2209,22 @@
         <v>0</v>
       </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2266,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6900</v>
       </c>
-      <c r="F26" s="3">
-        <v>-9900</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3">
         <v>-8800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-15500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3200</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
       <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6900</v>
       </c>
-      <c r="F27" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3">
         <v>-8800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-15500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6800</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>-2700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2542,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2634,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2726,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2818,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>-200</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>200</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-100</v>
       </c>
       <c r="Z32" s="3">
         <v>-100</v>
       </c>
       <c r="AA32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>1200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6900</v>
       </c>
-      <c r="F33" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3">
         <v>-8800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6800</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>-2700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3094,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6900</v>
       </c>
-      <c r="F35" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3">
         <v>-8800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6800</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>-2700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3317,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,83 +3437,84 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E41" s="3">
         <v>83700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>87200</v>
       </c>
-      <c r="F41" s="3">
-        <v>85800</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H41" s="3">
         <v>34700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>32200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>31900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>26800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>35100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>28800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>28200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>34100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>40400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>45500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>66400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>19200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>23300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>33600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>38700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>50400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9300</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3443,32 +3530,35 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>96500</v>
+      </c>
+      <c r="E42" s="3">
         <v>72600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>60700</v>
       </c>
-      <c r="F42" s="3">
-        <v>45900</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>10100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3900</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -3476,50 +3566,50 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>9900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>9000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>10300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>12300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>6900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>12500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>4400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1300</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3535,83 +3625,86 @@
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E43" s="3">
         <v>8000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2600</v>
       </c>
-      <c r="F43" s="3">
-        <v>6800</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
         <v>3000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>14200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>23200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>21200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>9400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4400</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3627,83 +3720,86 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E44" s="3">
         <v>13100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9700</v>
       </c>
-      <c r="F44" s="3">
-        <v>9800</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3">
         <v>8600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10200</v>
-      </c>
-      <c r="M44" s="3">
-        <v>11000</v>
       </c>
       <c r="N44" s="3">
         <v>11000</v>
       </c>
       <c r="O44" s="3">
+        <v>11000</v>
+      </c>
+      <c r="P44" s="3">
         <v>11800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>9400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1300</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3719,83 +3815,86 @@
       <c r="AF44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E45" s="3">
         <v>7600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10000</v>
       </c>
-      <c r="F45" s="3">
-        <v>7300</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>3700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3900</v>
-      </c>
-      <c r="T45" s="3">
-        <v>3300</v>
       </c>
       <c r="U45" s="3">
         <v>3300</v>
       </c>
       <c r="V45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="W45" s="3">
         <v>3000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3500</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3811,83 +3910,86 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>179600</v>
+      </c>
+      <c r="E46" s="3">
         <v>185900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>170200</v>
       </c>
-      <c r="F46" s="3">
-        <v>155500</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3">
         <v>60200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>63900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>58500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>40800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>51200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>54600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>51900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>56800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>58600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>65900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>78600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>86200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>93300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>59100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>68600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>60200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>57400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>67100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>25000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>19800</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3903,73 +4005,76 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E47" s="3">
         <v>4600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3200</v>
       </c>
-      <c r="F47" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
         <v>2500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2800</v>
-      </c>
-      <c r="M47" s="3">
-        <v>1400</v>
       </c>
       <c r="N47" s="3">
         <v>1400</v>
       </c>
       <c r="O47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P47" s="3">
         <v>1100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2400</v>
-      </c>
-      <c r="R47" s="3">
-        <v>2300</v>
       </c>
       <c r="S47" s="3">
         <v>2300</v>
       </c>
       <c r="T47" s="3">
+        <v>2300</v>
+      </c>
+      <c r="U47" s="3">
         <v>2500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7500</v>
-      </c>
-      <c r="X47" s="3">
-        <v>500</v>
       </c>
       <c r="Y47" s="3">
         <v>500</v>
@@ -3977,8 +4082,8 @@
       <c r="Z47" s="3">
         <v>500</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>3</v>
+      <c r="AA47" s="3">
+        <v>500</v>
       </c>
       <c r="AB47" s="3" t="s">
         <v>3</v>
@@ -3995,83 +4100,86 @@
       <c r="AF47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E48" s="3">
         <v>25800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23900</v>
       </c>
-      <c r="F48" s="3">
-        <v>22400</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3">
         <v>18800</v>
-      </c>
-      <c r="H48" s="3">
-        <v>16800</v>
       </c>
       <c r="I48" s="3">
         <v>16800</v>
       </c>
       <c r="J48" s="3">
+        <v>16800</v>
+      </c>
+      <c r="K48" s="3">
         <v>16200</v>
-      </c>
-      <c r="K48" s="3">
-        <v>17000</v>
       </c>
       <c r="L48" s="3">
         <v>17000</v>
       </c>
       <c r="M48" s="3">
+        <v>17000</v>
+      </c>
+      <c r="N48" s="3">
         <v>16000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2300</v>
-      </c>
-      <c r="X48" s="3">
-        <v>2500</v>
       </c>
       <c r="Y48" s="3">
         <v>2500</v>
       </c>
       <c r="Z48" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AA48" s="3">
         <v>2700</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4087,8 +4195,11 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4096,16 +4207,16 @@
         <v>400</v>
       </c>
       <c r="E49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F49" s="3">
         <v>300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3">
         <v>400</v>
-      </c>
-      <c r="H49" s="3">
-        <v>300</v>
       </c>
       <c r="I49" s="3">
         <v>300</v>
@@ -4120,10 +4231,10 @@
         <v>300</v>
       </c>
       <c r="M49" s="3">
+        <v>300</v>
+      </c>
+      <c r="N49" s="3">
         <v>200</v>
-      </c>
-      <c r="N49" s="3">
-        <v>100</v>
       </c>
       <c r="O49" s="3">
         <v>100</v>
@@ -4144,7 +4255,7 @@
         <v>100</v>
       </c>
       <c r="U49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V49" s="3">
         <v>200</v>
@@ -4156,13 +4267,13 @@
         <v>200</v>
       </c>
       <c r="Y49" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z49" s="3">
         <v>100</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
+      <c r="AA49" s="3">
+        <v>0</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>3</v>
@@ -4179,8 +4290,11 @@
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4271,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4363,13 +4480,16 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>1700</v>
       </c>
       <c r="E52" s="3">
         <v>300</v>
@@ -4377,8 +4497,8 @@
       <c r="F52" s="3">
         <v>300</v>
       </c>
-      <c r="G52" s="3">
-        <v>200</v>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
@@ -4402,7 +4522,7 @@
         <v>200</v>
       </c>
       <c r="O52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P52" s="3">
         <v>300</v>
@@ -4411,16 +4531,16 @@
         <v>300</v>
       </c>
       <c r="R52" s="3">
+        <v>300</v>
+      </c>
+      <c r="S52" s="3">
         <v>500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2800</v>
-      </c>
-      <c r="U52" s="3">
-        <v>100</v>
       </c>
       <c r="V52" s="3">
         <v>100</v>
@@ -4437,8 +4557,8 @@
       <c r="Z52" s="3">
         <v>100</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
+      <c r="AA52" s="3">
+        <v>100</v>
       </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
@@ -4455,8 +4575,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4547,83 +4670,86 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>220600</v>
+      </c>
+      <c r="E54" s="3">
         <v>217100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>198000</v>
       </c>
-      <c r="F54" s="3">
-        <v>180900</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3">
         <v>82100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>84400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>79100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>60500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>71200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>74800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>69700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>65600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>67400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>73900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>86500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>94000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>103100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>67400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>73200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>69500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>67400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>70400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>28000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>23000</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4639,8 +4765,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4707,83 +4837,84 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E57" s="3">
         <v>17500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14900</v>
       </c>
-      <c r="F57" s="3">
-        <v>10200</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3">
         <v>5800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>4600</v>
       </c>
       <c r="J57" s="3">
         <v>4600</v>
       </c>
       <c r="K57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="L57" s="3">
         <v>4700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5500</v>
-      </c>
-      <c r="P57" s="3">
-        <v>6300</v>
       </c>
       <c r="Q57" s="3">
         <v>6300</v>
       </c>
       <c r="R57" s="3">
-        <v>5100</v>
+        <v>6300</v>
       </c>
       <c r="S57" s="3">
         <v>5100</v>
       </c>
       <c r="T57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="U57" s="3">
         <v>7400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2600</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4799,70 +4930,73 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E58" s="3">
         <v>12000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>25700</v>
       </c>
-      <c r="F58" s="3">
-        <v>23900</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3">
         <v>7000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>1400</v>
       </c>
       <c r="R58" s="3">
         <v>1400</v>
       </c>
       <c r="S58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T58" s="3">
         <v>2200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1500</v>
-      </c>
-      <c r="W58" s="3">
-        <v>800</v>
       </c>
       <c r="X58" s="3">
         <v>800</v>
@@ -4871,11 +5005,11 @@
         <v>800</v>
       </c>
       <c r="Z58" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA58" s="3">
         <v>1600</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4891,83 +5025,86 @@
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E59" s="3">
         <v>17900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13800</v>
       </c>
-      <c r="F59" s="3">
-        <v>24900</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>6600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10800</v>
-      </c>
-      <c r="T59" s="3">
-        <v>12500</v>
       </c>
       <c r="U59" s="3">
         <v>12500</v>
       </c>
       <c r="V59" s="3">
+        <v>12500</v>
+      </c>
+      <c r="W59" s="3">
         <v>7100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,83 +5120,86 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E60" s="3">
         <v>64400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>71300</v>
       </c>
-      <c r="F60" s="3">
-        <v>73200</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3">
         <v>30600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>43400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>39800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>24100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>20700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>17700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>18100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>22000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>22500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>13300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>15000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9300</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5075,83 +5215,86 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E61" s="3">
         <v>20000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18600</v>
       </c>
-      <c r="F61" s="3">
-        <v>18300</v>
-      </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>15100</v>
-      </c>
-      <c r="H61" s="3">
-        <v>11900</v>
       </c>
       <c r="I61" s="3">
         <v>11900</v>
       </c>
       <c r="J61" s="3">
+        <v>11900</v>
+      </c>
+      <c r="K61" s="3">
         <v>10200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>500</v>
-      </c>
-      <c r="M61" s="3">
-        <v>600</v>
       </c>
       <c r="N61" s="3">
         <v>600</v>
       </c>
       <c r="O61" s="3">
+        <v>600</v>
+      </c>
+      <c r="P61" s="3">
         <v>700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2300</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>2800</v>
       </c>
       <c r="R61" s="3">
         <v>2800</v>
       </c>
       <c r="S61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="T61" s="3">
         <v>2900</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>4600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>300</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5167,22 +5310,25 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1500</v>
       </c>
-      <c r="F62" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1100</v>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
         <v>1100</v>
@@ -5191,28 +5337,28 @@
         <v>1100</v>
       </c>
       <c r="J62" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="K62" s="3">
         <v>1000</v>
       </c>
       <c r="L62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M62" s="3">
         <v>11300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>1200</v>
       </c>
       <c r="R62" s="3">
         <v>1200</v>
@@ -5224,25 +5370,25 @@
         <v>1200</v>
       </c>
       <c r="U62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="V62" s="3">
         <v>1300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>800</v>
-      </c>
-      <c r="W62" s="3">
-        <v>900</v>
       </c>
       <c r="X62" s="3">
         <v>900</v>
       </c>
       <c r="Y62" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="Z62" s="3">
         <v>800</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
+      <c r="AA62" s="3">
+        <v>800</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
@@ -5259,8 +5405,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5351,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5443,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5535,83 +5690,86 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E66" s="3">
         <v>86100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>91500</v>
       </c>
-      <c r="F66" s="3">
-        <v>92900</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H66" s="3">
         <v>47000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>40500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>42100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>55400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>57300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>43300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>32800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>26600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>27500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>28100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>29000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>30100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>21600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10700</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5627,8 +5785,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5661,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5753,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5845,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5914,14 +6082,14 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>102400</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>100800</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -5937,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6029,83 +6200,86 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-284000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-271700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-276000</v>
       </c>
-      <c r="F72" s="3">
-        <v>-259800</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3">
         <v>-251600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-247300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-230400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-222500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-224000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-204300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-185000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-175600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-164300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-154800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-144400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-134100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-124800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-112300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-111700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-111600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-116600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-112600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-108400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-105100</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6121,8 +6295,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6213,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6305,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6397,83 +6580,86 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>127100</v>
+      </c>
+      <c r="E76" s="3">
         <v>130900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>106400</v>
       </c>
-      <c r="F76" s="3">
-        <v>87900</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H76" s="3">
         <v>29500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>30200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>33000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>26400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>32700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>37800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>45900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>59900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>66500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>75100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>38500</v>
-      </c>
-      <c r="U76" s="3">
-        <v>43100</v>
       </c>
       <c r="V76" s="3">
         <v>43100</v>
       </c>
       <c r="W76" s="3">
+        <v>43100</v>
+      </c>
+      <c r="X76" s="3">
         <v>47800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>48800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-91000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-88500</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6489,8 +6675,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6581,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6900</v>
       </c>
-      <c r="F81" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3">
         <v>-8800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6800</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>-2700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6804,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6833,8 +7032,8 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -6842,62 +7041,65 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3">
         <v>500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>-600</v>
-      </c>
-      <c r="X83" s="3">
-        <v>200</v>
       </c>
       <c r="Y83" s="3">
         <v>200</v>
       </c>
       <c r="Z83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA83" s="3">
         <v>400</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>200</v>
       </c>
       <c r="AB83" s="3">
         <v>200</v>
       </c>
       <c r="AC83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD83" s="3">
         <v>400</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6988,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7080,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7172,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7264,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7356,8 +7570,11 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7385,8 +7602,8 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -7394,62 +7611,65 @@
       <c r="N89" s="3">
         <v>0</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3">
         <v>-6100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-21100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-10900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7482,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7511,8 +7732,8 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -7521,52 +7742,52 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-1200</v>
       </c>
       <c r="T91" s="3">
         <v>-1200</v>
       </c>
       <c r="U91" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA91" s="3">
         <v>-100</v>
       </c>
       <c r="AB91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="AC91" s="3">
         <v>-400</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
+      <c r="AD91" s="3">
+        <v>-400</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
@@ -7574,8 +7795,11 @@
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7666,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,8 +7985,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7787,8 +8017,8 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -7796,62 +8026,65 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3">
         <v>-7000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>3300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1300</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7884,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7913,8 +8147,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7976,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8068,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8160,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8252,8 +8495,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8281,8 +8527,8 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -8290,62 +8536,65 @@
       <c r="N100" s="3">
         <v>0</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>36900</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3">
         <v>38900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>40000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-51700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>39600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>7300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>7200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2100</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8373,8 +8622,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8382,85 +8631,88 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-700</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -8474,58 +8726,61 @@
       <c r="N102" s="3">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3">
         <v>14800</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3">
         <v>25600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>46300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-25300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-10400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-13800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-53100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>43100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-600</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
